--- a/public/f3-excel-v1.2.xlsx
+++ b/public/f3-excel-v1.2.xlsx
@@ -1122,7 +1122,9 @@
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="G19" s="11" t="n">
+        <v>46294.5</v>
+      </c>
     </row>
     <row r="20" ht="64" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -4071,7 +4073,9 @@
         </is>
       </c>
       <c r="F117" s="25" t="n"/>
-      <c r="G117" s="25" t="n"/>
+      <c r="G117" s="25" t="n">
+        <v>46294.5</v>
+      </c>
     </row>
     <row r="118" ht="64" customHeight="1">
       <c r="A118" s="9" t="inlineStr">

--- a/public/f3-excel-v1.2.xlsx
+++ b/public/f3-excel-v1.2.xlsx
@@ -311,10 +311,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:G140" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:G140"/>
-  <sortState ref="A2:G140">
-    <sortCondition ref="A1:A140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:G139" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:G139"/>
+  <sortState ref="A2:G139">
+    <sortCondition ref="A1:A139"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" name="Technique ID"/>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1503,30 +1503,30 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
     </row>
-    <row r="33" ht="48" customHeight="1">
+    <row r="33" ht="64" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>F1010</t>
+          <t>F1011</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Buy Money Order</t>
+          <t>Card Dump Capture</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may purchase money orders with stolen payment methods or fraudulent funds to convert illicit proceeds into more anonymous monetary instruments. Money orders can be cashed at various locations, are difficult to trace back to the purchaser, and can be used as payment instruments with reduced fraud detection compared to electronic payments.</t>
+          <t>Fraud actors may capture payment card magnetic stripe data, EMV chip data, or card details from various sources. This may include using skimming devices at point-of-sale terminals, ATMs, or fuel pumps, compromising payment processing systems, or conducting memory scraping attacks against POS systems. Captured card data can be used to create counterfeit cards, conduct card-not-present fraud, or be sold to other malicious fraud actors.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>FA0002</t>
+          <t>FA0001, TA0043</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Monetization</t>
+          <t>Positioning, Reconnaissance</t>
         </is>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -1535,27 +1535,27 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>F1011</t>
+          <t>F1012</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Card Dump Capture</t>
+          <t>Card Testing</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may capture payment card magnetic stripe data, EMV chip data, or card details from various sources. This may include using skimming devices at point-of-sale terminals, ATMs, or fuel pumps, compromising payment processing systems, or conducting memory scraping attacks against POS systems. Captured card data can be used to create counterfeit cards, conduct card-not-present fraud, or be sold to other malicious fraud actors.</t>
+          <t>Fraud actors may test stolen payment card credentials by conducting small transactions to determine if cards are valid and active. This may include making small purchases, authorization attempts without completing transactions, or using automated testing services. Successful card tests confirm which stolen credentials remain valid for use in larger fraudulent transactions or for sale to other malicious fraud actors.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>FA0001, TA0043</t>
+          <t>FA0001</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Positioning, Reconnaissance</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -1564,17 +1564,17 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>F1012</t>
+          <t>F1013</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Card Testing</t>
+          <t>Change Payroll Details</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may test stolen payment card credentials by conducting small transactions to determine if cards are valid and active. This may include making small purchases, authorization attempts without completing transactions, or using automated testing services. Successful card tests confirm which stolen credentials remain valid for use in larger fraudulent transactions or for sale to other malicious fraud actors.</t>
+          <t>Fraud actors may alter payroll or HR system settings so that an employee’s salary or wage payments are redirected to accounts they control. This typically involves changing direct‑deposit account and routing numbers, updating payee details, or modifying payroll profiles inside dedicated payroll/HR platforms, resulting in ongoing diversion of regular paycheck deposits away from the legitimate employee.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -1590,120 +1590,120 @@
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n"/>
     </row>
-    <row r="36" ht="64" customHeight="1">
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>F1013</t>
+          <t>F1014</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Change Payroll Details</t>
+          <t>Check Fraud</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may alter payroll or HR system settings so that an employee’s salary or wage payments are redirected to accounts they control. This typically involves changing direct‑deposit account and routing numbers, updating payee details, or modifying payroll profiles inside dedicated payroll/HR platforms, resulting in ongoing diversion of regular paycheck deposits away from the legitimate employee.</t>
+          <t>Fraud Actors may illicitly obtain funds by abusing paper or digital checks tied to existing accounts. This can involve stealing checks, forging signatures or endorsements, issuing counterfeit or unauthorized checks, altering payee or amount details, or “washing” and reusing legitimate checks, all with the goal of cashing out or redirecting funds without the account holder’s consent.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>FA0001</t>
+          <t>TA0002</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="F36" s="11" t="n"/>
       <c r="G36" s="11" t="n"/>
     </row>
-    <row r="37" ht="48" customHeight="1">
+    <row r="37" ht="160" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>F1014</t>
+          <t>F1015</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Check Fraud</t>
+          <t>Churning</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Fraud Actors may illicitly obtain funds by abusing paper or digital checks tied to existing accounts. This can involve stealing checks, forging signatures or endorsements, issuing counterfeit or unauthorized checks, altering payee or amount details, or “washing” and reusing legitimate checks, all with the goal of cashing out or redirecting funds without the account holder’s consent.</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>TA0002</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="160" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>F1015</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Churning</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Churning fraud occurs when fraud actors repeatedly use stolen payment card information to conduct transactions until the card limit is reached or the account balance is depleted, often before detection or card deactivation.
 Fraud actors typically begin with a low‑value test transaction to confirm that the card details are valid and active, then rapidly execute a series of higher‑value transactions. These transactions often involve card‑not‑present channels such as eCommerce, digital goods and services, or purchases that can be quickly resold, including gift cards, prepaid instruments, or other easily liquidated assets.
 The primary objectives of churning fraud are to quickly monetize stolen card data before it is revoked, acquire goods or assets that can be anonymized or converted into cash with minimal traceability, and maximize financial gain from each compromised card before fraud controls or victims detect the activity.</t>
         </is>
       </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>TA0002</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="144" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>F1016</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Compromise Payment Gateway</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Fraudsters may gain unauthorized access to payment gateway platforms that process online transactions, allowing them to interfere with how payments are routed and recorded. Once embedded in a gateway environment, they can redirect transactions to accounts they control, alter transaction details to siphon funds, capture payment card and customer data, or disrupt normal settlement processes.
+Compromise of a payment gateway can occur through exploitation of software vulnerabilities, use of stolen or weak credentials, phishing of gateway or merchant staff, or deployment of malware that intercepts traffic between merchants and the gateway. Fraud actors often focus on weaknesses in the integration between a merchant’s website and the gateway, or on misconfigurations and security gaps within the gateway’s own infrastructure, to maintain persistent and covert access.</t>
+        </is>
+      </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>TA0002</t>
+          <t>TA0001</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Initial Access</t>
         </is>
       </c>
       <c r="F38" s="11" t="n"/>
       <c r="G38" s="11" t="n"/>
     </row>
-    <row r="39" ht="144" customHeight="1">
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>F1016</t>
+          <t>F1017</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Compromise Payment Gateway</t>
+          <t>Conversion to Physical Monetary Instruments</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Fraudsters may gain unauthorized access to payment gateway platforms that process online transactions, allowing them to interfere with how payments are routed and recorded. Once embedded in a gateway environment, they can redirect transactions to accounts they control, alter transaction details to siphon funds, capture payment card and customer data, or disrupt normal settlement processes.
-Compromise of a payment gateway can occur through exploitation of software vulnerabilities, use of stolen or weak credentials, phishing of gateway or merchant staff, or deployment of malware that intercepts traffic between merchants and the gateway. Fraud actors often focus on weaknesses in the integration between a merchant’s website and the gateway, or on misconfigurations and security gaps within the gateway’s own infrastructure, to maintain persistent and covert access.</t>
+          <t>Fraud actors may turn digital or account‑based balances into physical money or negotiable instruments to complete cash‑out. By moving value into cash or cash‑like forms, they reduce traceability within electronic payment systems and gain flexibility to spend, transport, or further launder proceeds.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>TA0001</t>
+          <t>FA0002</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Initial Access</t>
+          <t>Monetization</t>
         </is>
       </c>
       <c r="F39" s="11" t="n"/>
@@ -1712,17 +1712,17 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>F1017</t>
+          <t>F1017.001</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Conversion to Physical Monetary Instruments</t>
+          <t>Conversion to Physical Monetary Instruments: Cash</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may turn digital or account‑based balances into physical money or negotiable instruments to complete cash‑out. By moving value into cash or cash‑like forms, they reduce traceability within electronic payment systems and gain flexibility to spend, transport, or further launder proceeds.</t>
+          <t>Fraud actors may withdraw cash directly from compromised accounts using ATMs, in‑branch teller withdrawals, or cash‑back at point‑of‑sale. Cash withdrawals provide immediate access to funds and can be coordinated across multiple mules, cards, or locations to rapidly deplete balances before controls or fraud‑detection mechanisms respond.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -1741,17 +1741,17 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>F1017.001</t>
+          <t>F1017.002</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Conversion to Physical Monetary Instruments: Cash</t>
+          <t>Conversion to Physical Monetary Instruments: Cashier's Check</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may withdraw cash directly from compromised accounts using ATMs, in‑branch teller withdrawals, or cash‑back at point‑of‑sale. Cash withdrawals provide immediate access to funds and can be coordinated across multiple mules, cards, or locations to rapidly deplete balances before controls or fraud‑detection mechanisms respond.</t>
+          <t>Fraud actors may request cashier’s checks funded from compromised accounts and payable to themselves, accomplices, or front entities. Once issued, cashier’s checks can be deposited, cashed, or used to purchase high‑value goods, providing a semi‑anonymous way to move and store value outside the original account.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -1770,17 +1770,17 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>F1017.002</t>
+          <t>F1017.003</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Conversion to Physical Monetary Instruments: Cashier's Check</t>
+          <t>Conversion to Physical Monetary Instruments: Money Order</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may request cashier’s checks funded from compromised accounts and payable to themselves, accomplices, or front entities. Once issued, cashier’s checks can be deposited, cashed, or used to purchase high‑value goods, providing a semi‑anonymous way to move and store value outside the original account.</t>
+          <t>Fraud actors may purchase money orders using funds drawn from compromised accounts, including via debit card, bank counter transactions, or other payment instruments. Money orders can then be cashed, resold, or used for payments (such as rent or goods), enabling further layering and obscuring the link to the original compromised account.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>F1017.003</t>
+          <t>F1018</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Conversion to Physical Monetary Instruments: Money Order</t>
+          <t>Convert to Cryptocurrency</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may purchase money orders using funds drawn from compromised accounts, including via debit card, bank counter transactions, or other payment instruments. Money orders can then be cashed, resold, or used for payments (such as rent or goods), enabling further layering and obscuring the link to the original compromised account.</t>
+          <t>Fraudsters may convert stolen or illicit funds into cryptocurrencies such as Bitcoin or Ethereum to obscure the origin and movement of value. Cryptocurrency transfers leverage pseudonymous addresses and cross‑platform exchanges, making it more difficult for traditional financial monitoring and investigative processes to trace or recover the underlying funds.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -1828,27 +1828,27 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>F1018</t>
+          <t>F1019</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Convert to Cryptocurrency</t>
+          <t>Create Counterfeit Card</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Fraudsters may convert stolen or illicit funds into cryptocurrencies such as Bitcoin or Ethereum to obscure the origin and movement of value. Cryptocurrency transfers leverage pseudonymous addresses and cross‑platform exchanges, making it more difficult for traditional financial monitoring and investigative processes to trace or recover the underlying funds.</t>
+          <t>Fraudsters may manufacture physical payment cards using stolen or fabricated card data in order to conduct in‑person or card‑present transactions. This includes encoding compromised account details onto blank card stock or cloning existing cards so that fraudulent purchases, ATM withdrawals, or cash‑back transactions appear to originate from a legitimate debit or credit card.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>FA0002</t>
+          <t>TA0042</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Monetization</t>
+          <t>Resource Development</t>
         </is>
       </c>
       <c r="F44" s="11" t="n"/>
@@ -1857,17 +1857,17 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>F1019</t>
+          <t>F1020</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Create Counterfeit Card</t>
+          <t>Create Fake Materials</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Fraudsters may manufacture physical payment cards using stolen or fabricated card data in order to conduct in‑person or card‑present transactions. This includes encoding compromised account details onto blank card stock or cloning existing cards so that fraudulent purchases, ATM withdrawals, or cash‑back transactions appear to originate from a legitimate debit or credit card.</t>
+          <t>Fraud actors may create fraudulent materials to deceive victims or establish false legitimacy. This may include creating fake websites, fraudulent documents, counterfeit identification, or other materials designed to appear legitimate. Fake materials are used to support various fraud operations including phishing, identity fraud, business email compromise, or establishing fraudulent business entities.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -1883,20 +1883,20 @@
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="11" t="n"/>
     </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>F1020</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Create Fake Materials</t>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>F1020.001</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>Create Fake Materials: Fake Documents</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may create fraudulent materials to deceive victims or establish false legitimacy. This may include creating fake websites, fraudulent documents, counterfeit identification, or other materials designed to appear legitimate. Fake materials are used to support various fraud operations including phishing, identity fraud, business email compromise, or establishing fraudulent business entities.</t>
+          <t>Fraud actors may forge documents and supporting artifacts to falsify identities, deceive authorities, or fabricate evidence in support of fraud operations. This can include creating or altering identification cards, passports, financial statements, or shipping-related evidence such as tracking numbers to bypass verification processes, gain access to restricted services, or legitimize fraudulent transactions. Commonly faked documents include bank statements, paychecks, government-issued IDs, Social Security cards, insurance policies, invoices, business licenses, which may be either fully counterfeit or subtly modified to evade detection.</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -1912,20 +1912,21 @@
       <c r="F46" s="11" t="n"/>
       <c r="G46" s="11" t="n"/>
     </row>
-    <row r="47" ht="80" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
-        <is>
-          <t>F1020.001</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>Create Fake Materials: Fake Documents</t>
+    <row r="47" ht="128" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>F1020.002</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Create Fake Materials: Fake Website</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may forge documents and supporting artifacts to falsify identities, deceive authorities, or fabricate evidence in support of fraud operations. This can include creating or altering identification cards, passports, financial statements, or shipping-related evidence such as tracking numbers to bypass verification processes, gain access to restricted services, or legitimize fraudulent transactions. Commonly faked documents include bank statements, paychecks, government-issued IDs, Social Security cards, insurance policies, invoices, business licenses, which may be either fully counterfeit or subtly modified to evade detection.</t>
+          <t>Fraud actors may create fraudulent e-commerce websites that mimic legitimate retailers to capture payment information or steal credentials. This may include replicating the design, layout, and functionality of trusted sites while hosting them on attacker-controlled infrastructure, often using lookalike domains (e.g., typosquatting) to appear legitimate. Fraud actors may advertise products with no intention of delivery to harvest payment card information during checkout.
+Fraud actors may promote these sites through phishing campaigns, malicious advertisements, search engine optimization, or social media to drive victim traffic. Fraud actors use these sites to collect credentials, payment details, or personal data, redirect transactions, or facilitate additional fraudulent activity.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -1941,50 +1942,53 @@
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="11" t="n"/>
     </row>
-    <row r="48" ht="128" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>F1020.002</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Create Fake Materials: Fake Website</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may create fraudulent e-commerce websites that mimic legitimate retailers to capture payment information or steal credentials. This may include replicating the design, layout, and functionality of trusted sites while hosting them on attacker-controlled infrastructure, often using lookalike domains (e.g., typosquatting) to appear legitimate. Fraud actors may advertise products with no intention of delivery to harvest payment card information during checkout.
-Fraud actors may promote these sites through phishing campaigns, malicious advertisements, search engine optimization, or social media to drive victim traffic. Fraud actors use these sites to collect credentials, payment details, or personal data, redirect transactions, or facilitate additional fraudulent activity.</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>F1020.003</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Create Fake Materials: Synthetic Media</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Fraud actors may create or manipulate synthetic audio, video, images, or other media to impersonate a person, fabricate an identity, or support a fraudulent pretext. This may include deepfake video, generated identity images, cloned or altered voices, or real-time media manipulation. Fraud actors may use synthetic media to deceive victims and employees, bypass liveness or biometric verification, or convince targets to disclose information or authorize transactions.</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="21" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="64" customHeight="1">
+      <c r="F48" s="23" t="n">
+        <v>46255.5</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>46255.5</v>
+      </c>
+    </row>
+    <row r="49" ht="80" customHeight="1">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>F1020.003</t>
+          <t>F1020.004</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>Create Fake Materials: Synthetic Media</t>
+          <t>Create Fake Materials: Spoofed Application</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Fraud actors may create or manipulate synthetic audio, video, images, or other media to impersonate a person, fabricate an identity, or support a fraudulent pretext. This may include deepfake video, generated identity images, cloned or altered voices, or real-time media manipulation. Fraud actors may use synthetic media to deceive victims and employees, bypass liveness or biometric verification, or convince targets to disclose information or authorize transactions.</t>
+          <t>Fraud actors may create applications that mimic legitimate financial, investment, cryptocurrency, merchant, government, or service-provider applications. Spoofed applications may copy trusted branding, interfaces, workflows, and account information to deceive victims into entering credentials, payment data, personal information, or transferring funds. Fraud actors may distribute these applications through unofficial download sites, malicious links, third-party stores, or compromised accounts and may use them to support phishing, account takeover, or fraudulent investment schemes.</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -2004,83 +2008,79 @@
         <v>46255.5</v>
       </c>
     </row>
-    <row r="50" ht="80" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>F1020.004</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>Create Fake Materials: Spoofed Application</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>Fraud actors may create applications that mimic legitimate financial, investment, cryptocurrency, merchant, government, or service-provider applications. Spoofed applications may copy trusted branding, interfaces, workflows, and account information to deceive victims into entering credentials, payment data, personal information, or transferring funds. Fraud actors may distribute these applications through unofficial download sites, malicious links, third-party stores, or compromised accounts and may use them to support phishing, account takeover, or fraudulent investment schemes.</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>TA0042</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>Resource Development</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>46255.5</v>
-      </c>
-      <c r="G50" s="23" t="n">
-        <v>46255.5</v>
-      </c>
-    </row>
-    <row r="51" ht="128" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="50" ht="128" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>F1021</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Create Fraudulent Merchant Account</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may create fraudulent merchant accounts with payment processors or acquiring banks to obtain legitimate‑appearing payment acceptance capabilities. These accounts are often opened using stolen or fabricated identity information, shell businesses, or front companies to bypass onboarding and KYC controls.
 Once established, fraudulent merchant accounts allow fraud actors to process payments for non‑existent or sham goods and services, run payment card testing at scale, or move and cycle funds as part of broader fraud schemes. By mimicking the behavior and documentation of real merchants, these accounts provide a controlled point for receiving card payments and disbursing proceeds, while making downstream transactions appear to originate from a legitimate business.</t>
         </is>
       </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>TA0042</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Resource Development</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>F1022</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Delete Relevant Emails</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Fraudsters may delete emails that could alert victims or investigators to ongoing fraudulent activity. This can include removing copies of messages sent from the victim’s account, replies from recipients, security alerts about unusual login or transaction activity, or other notifications that would reveal account changes, preventing the legitimate user from noticing and responding to the compromise</t>
+        </is>
+      </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>TA0042</t>
+          <t>TA0005</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Resource Development</t>
+          <t>Stealth</t>
         </is>
       </c>
       <c r="F51" s="11" t="n"/>
       <c r="G51" s="11" t="n"/>
     </row>
-    <row r="52" ht="48" customHeight="1">
+    <row r="52" ht="64" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>F1022</t>
+          <t>F1023</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Delete Relevant Emails</t>
+          <t>Device Fingerprint Spoofing</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Fraudsters may delete emails that could alert victims or investigators to ongoing fraudulent activity. This can include removing copies of messages sent from the victim’s account, replies from recipients, security alerts about unusual login or transaction activity, or other notifications that would reveal account changes, preventing the legitimate user from noticing and responding to the compromise</t>
+          <t>Fraud actors employ device fingerprint spoofing to mask their true identities and evade detection by security systems. By manipulating various attributes of their device's fingerprint, such as browser settings, operating system details, and hardware configurations, they can make their devices appear as different, legitimate ones. This technique enables fraud actors to bypass security measures that rely on device identification for authentication or fraud detection, allowing them to carry out illicit activities while remaining undetected.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2096,107 +2096,107 @@
       <c r="F52" s="11" t="n"/>
       <c r="G52" s="11" t="n"/>
     </row>
-    <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>F1023</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Device Fingerprint Spoofing</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors employ device fingerprint spoofing to mask their true identities and evade detection by security systems. By manipulating various attributes of their device's fingerprint, such as browser settings, operating system details, and hardware configurations, they can make their devices appear as different, legitimate ones. This technique enables fraud actors to bypass security measures that rely on device identification for authentication or fraud detection, allowing them to carry out illicit activities while remaining undetected.</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>TA0005</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>F1024</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Dispute Legitimate Transaction</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Fraud Actors or complicit consumers may intentionally dispute legitimate card purchases or payment transactions to obtain unwarranted credits or refunds from a financial institution. By falsely claiming that a transaction was unauthorized, fraudulent, or that goods or services were not received, they seek to reverse charges while retaining the benefit of the original purchase.</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>TA0002</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
     </row>
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>F1024</t>
+          <t>F1025</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Dispute Legitimate Transaction</t>
+          <t>Electronic Funds Transfer</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>Fraud Actors or complicit consumers may intentionally dispute legitimate card purchases or payment transactions to obtain unwarranted credits or refunds from a financial institution. By falsely claiming that a transaction was unauthorized, fraudulent, or that goods or services were not received, they seek to reverse charges while retaining the benefit of the original purchase.</t>
+          <t>Fraud actors may use electronic funds transfer mechanisms to move money out of compromised accounts into destinations they control. This activity can leverage traditional banking rails, regional payment systems, or peer‑to‑peer platforms to rapidly cash out or further obscure stolen funds.</t>
         </is>
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>TA0002</t>
+          <t>FA0002</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Monetization</t>
         </is>
       </c>
       <c r="F54" s="24" t="n"/>
       <c r="G54" s="24" t="n"/>
     </row>
     <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>F1025</t>
-        </is>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>Electronic Funds Transfer</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors may use electronic funds transfer mechanisms to move money out of compromised accounts into destinations they control. This activity can leverage traditional banking rails, regional payment systems, or peer‑to‑peer platforms to rapidly cash out or further obscure stolen funds.</t>
-        </is>
-      </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>F1025.001</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Electronic Funds Transfer: Peer-to-Peer Transfer</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may use regional payment systems, such as ACH or SEPA, to schedule push payments, credits, or other electronic transfers from victim accounts to accounts they or their accomplices control. These rails can support repeated or batched withdrawals, enabling lower‑value but high‑volume monetization that may initially blend into normal transaction patterns.</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>FA0002</t>
         </is>
       </c>
-      <c r="E55" s="19" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>Monetization</t>
         </is>
       </c>
-      <c r="F55" s="24" t="n"/>
-      <c r="G55" s="24" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
     </row>
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>F1025.001</t>
+          <t>F1025.002</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Electronic Funds Transfer: Peer-to-Peer Transfer</t>
+          <t>Electronic Funds Transfer: Regional Payment Rail</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may use regional payment systems, such as ACH or SEPA, to schedule push payments, credits, or other electronic transfers from victim accounts to accounts they or their accomplices control. These rails can support repeated or batched withdrawals, enabling lower‑value but high‑volume monetization that may initially blend into normal transaction patterns.</t>
+          <t>Fraudsters may convert compromised account balances into physical funds by obtaining cash or cash‑like instruments, including ATM withdrawals, cashier’s checks, money orders, or similar negotiable instruments. Physical withdrawals allow immediate spending or further layering of funds outside of the original financial channel</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -2215,17 +2215,17 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>F1025.002</t>
+          <t>F1025.003</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Electronic Funds Transfer: Regional Payment Rail</t>
+          <t>Electronic Funds Transfer: Wire Transfer</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Fraudsters may convert compromised account balances into physical funds by obtaining cash or cash‑like instruments, including ATM withdrawals, cashier’s checks, money orders, or similar negotiable instruments. Physical withdrawals allow immediate spending or further layering of funds outside of the original financial channel</t>
+          <t>Fraud actors may initiate domestic or international wire transfers from compromised accounts to mule or controlled accounts. Wire transfers can move large values quickly and, once executed, are often difficult or slow to reverse, providing an efficient channel for high‑value cash‑out.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2241,20 +2241,21 @@
       <c r="F57" s="11" t="n"/>
       <c r="G57" s="11" t="n"/>
     </row>
-    <row r="58" ht="48" customHeight="1">
+    <row r="58" ht="144" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>F1025.003</t>
+          <t>F1026</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Electronic Funds Transfer: Wire Transfer</t>
+          <t>Exploitation of Gambling Platforms</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may initiate domestic or international wire transfers from compromised accounts to mule or controlled accounts. Wire transfers can move large values quickly and, once executed, are often difficult or slow to reverse, providing an efficient channel for high‑value cash‑out.</t>
+          <t>Fraud actors may exploit gambling platforms as a channel to convert illicit value into seemingly legitimate funds and to move or disguise the proceeds of fraud. They may create or use accounts, often opened with stolen or fabricated identities, to deposit illicit funds, place low‑risk or offsetting bets, and then withdraw balances as “winnings” to other accounts under their control. They may also exploit bonus structures, loyalty rewards, or promotional credits to generate additional value, or conduct arbitrage across multiple platforms to turn promotional or gaming flows into profit. 
+By routing funds through gambling platforms and generating complex patterns of bets, transfers, and payouts, actors aim to obscure the source of the money and make subsequent withdrawals appear consistent with normal gambling activity, supporting monetization and money‑laundering objectives rather than the initial execution of fraud.</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -2270,77 +2271,47 @@
       <c r="F58" s="11" t="n"/>
       <c r="G58" s="11" t="n"/>
     </row>
-    <row r="59" ht="144" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>F1026</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Exploitation of Gambling Platforms</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may exploit gambling platforms as a channel to convert illicit value into seemingly legitimate funds and to move or disguise the proceeds of fraud. They may create or use accounts, often opened with stolen or fabricated identities, to deposit illicit funds, place low‑risk or offsetting bets, and then withdraw balances as “winnings” to other accounts under their control. They may also exploit bonus structures, loyalty rewards, or promotional credits to generate additional value, or conduct arbitrage across multiple platforms to turn promotional or gaming flows into profit. 
-By routing funds through gambling platforms and generating complex patterns of bets, transfers, and payouts, actors aim to obscure the source of the money and make subsequent withdrawals appear consistent with normal gambling activity, supporting monetization and money‑laundering objectives rather than the initial execution of fraud.</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>FA0002</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Monetization</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="n"/>
-      <c r="G59" s="11" t="n"/>
-    </row>
-    <row r="60" ht="64" customHeight="1">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>F1027</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>Falsify Business Documents</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may create or alter business documents to support fraud schemes or deceive stakeholders. This may include creating fake invoices, forging business licenses, falsifying financial statements, or creating fraudulent corporate documentation. Falsified documents may be used to establish fraudulent business entities, support business email compromise schemes, obtain financing, or deceive partners and customers.</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F60" s="24" t="n"/>
-      <c r="G60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="256" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="F59" s="24" t="n"/>
+      <c r="G59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="256" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>F1028</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Fradulent Purchasing</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Fraudulent purchasing occurs when fraud actors use stolen payment card data, compromised or fraudulent accounts, or money laundering channels to buy goods or services. These purchases are used to convert illicit funds into seemingly legitimate assets, avoid scrutiny by financial institutions, or cash out stolen value into clean money.
 Fraud actors may carry out fraudulent purchases using stolen credit card details or by abusing compromised financial accounts on e‑commerce platforms, payment processors (for example, gateway providers), or brick‑and‑mortar merchants with online payment capabilities. They may prioritize high‑value goods that can be quickly resold, or convert funds into cryptocurrencies or gift cards that provide liquid, harder‑to‑trace value.
@@ -2348,73 +2319,102 @@
 The primary objectives of fraudulent purchasing are to liquidate stolen financial assets before detection and account shutdown, launder money by transforming illicit funds into physical goods that can be resold for “clean” proceeds, and obtain goods or services for personal use or profit without any intention of legitimate payment.</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>TA0002, FA0002</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Execution, Monetization</t>
         </is>
       </c>
-      <c r="F61" s="11" t="n"/>
-      <c r="G61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="160" customHeight="1">
-      <c r="A62" s="19" t="inlineStr">
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="160" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>F1029</t>
         </is>
       </c>
-      <c r="B62" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>Gather Customer Information</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may gather information about existing or prospective customers to support targeted fraud operations and social‑engineering attacks against financial institutions, merchants, or platforms. This can include collecting customer identity details (such as names, addresses, dates of birth, government identifiers), account and card data, contact information, relationship data (for example, employers, family members, or business associations), and behavioral or preference information (such as typical spending patterns or channel usage).
 Customer information may be sourced from data breaches, underground markets, public records, social media, third‑party data brokers, compromised internal systems, or direct social‑engineering of customers and staff. Aggregated customer data enables more convincing impersonation, tailored fraud scenarios, and higher‑success attacks such as account takeover, new‑account fraud, mule recruitment, and highly targeted social‑engineering campaigns against both customers and the institutions that serve them.</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>TA0043</t>
         </is>
       </c>
-      <c r="E62" s="19" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>Reconnaissance</t>
         </is>
       </c>
-      <c r="F62" s="24" t="n"/>
-      <c r="G62" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>F1030</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Geolocation Spoofing</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may falsify geographic location information to bypass location-based security controls or access restricted services. This may include using VPNs, proxy servers, GPS spoofing applications, or other techniques to mask true location. Location spoofing allows fraud actors to access geo-restricted content, bypass location-based fraud detection, or hide their true location during fraud operations.</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>TA0005</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
     </row>
     <row r="63" ht="64" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>F1030</t>
+          <t>F1031</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Geolocation Spoofing</t>
+          <t>Impersonate Account Holder</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may falsify geographic location information to bypass location-based security controls or access restricted services. This may include using VPNs, proxy servers, GPS spoofing applications, or other techniques to mask true location. Location spoofing allows fraud actors to access geo-restricted content, bypass location-based fraud detection, or hide their true location during fraud operations.</t>
+          <t>Fraud actors may impersonate legitimate account holders when interacting with financial institutions or service providers. This may include using stolen personal information to answer authentication questions, conducting social engineering attacks while impersonating victims, or using compromised identity information to convince institutions to grant access or conduct transactions. Successful impersonation can bypass identity verification controls.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>TA0005</t>
+          <t>TA0001, TA0005</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Initial Access, Stealth</t>
         </is>
       </c>
       <c r="F63" s="11" t="n"/>
@@ -2423,17 +2423,17 @@
     <row r="64" ht="64" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>F1031</t>
+          <t>F1032</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Impersonate Account Holder</t>
+          <t>Impersonate Official</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may impersonate legitimate account holders when interacting with financial institutions or service providers. This may include using stolen personal information to answer authentication questions, conducting social engineering attacks while impersonating victims, or using compromised identity information to convince institutions to grant access or conduct transactions. Successful impersonation can bypass identity verification controls.</t>
+          <t>Fraud actors may impersonate officials such as bank representatives, law enforcement officers, government agents, or other authority figures to manipulate victims. By impersonating officials, fraud actors leverage the trust and authority associated with these positions to convince victims to provide sensitive information, authorize transactions, or take actions that facilitate fraud. Impersonation may occur through phone calls, emails, or in-person interactions.</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2449,281 +2449,281 @@
       <c r="F64" s="11" t="n"/>
       <c r="G64" s="11" t="n"/>
     </row>
-    <row r="65" ht="64" customHeight="1">
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>F1032</t>
+          <t>F1033</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Impersonate Official</t>
+          <t>Insider Access Abuse</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may impersonate officials such as bank representatives, law enforcement officers, government agents, or other authority figures to manipulate victims. By impersonating officials, fraud actors leverage the trust and authority associated with these positions to convince victims to provide sensitive information, authorize transactions, or take actions that facilitate fraud. Impersonation may occur through phone calls, emails, or in-person interactions.</t>
+          <t>Fraud actors may abuse legitimate access privileges to conduct fraud operations. This may include malicious insiders, compromised insiders, or exploitation of excessive access privileges by authorized users. Insider access provides fraud actors with legitimate credentials and authorization to access systems, data, or conduct transactions, making detection more difficult than external attacks.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>TA0001, TA0005</t>
+          <t>TA0001</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Initial Access, Stealth</t>
+          <t>Initial Access</t>
         </is>
       </c>
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="11" t="n"/>
     </row>
-    <row r="66" ht="48" customHeight="1">
+    <row r="66" ht="64" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>F1033</t>
+          <t>F1034</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Insider Access Abuse</t>
+          <t>Interactive Voice Response Mapping</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may abuse legitimate access privileges to conduct fraud operations. This may include malicious insiders, compromised insiders, or exploitation of excessive access privileges by authorized users. Insider access provides fraud actors with legitimate credentials and authorization to access systems, data, or conduct transactions, making detection more difficult than external attacks.</t>
+          <t>Fraud actors may interact with interactive voice response systems to understand call flows, authentication mechanisms, or available functions. By mapping IVR systems, fraud actors can identify opportunities for fraud, understand authentication requirements, or develop strategies for social engineering attacks against customer service representatives. IVR discovery may be automated or conducted manually to gather intelligence for fraud operations.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>TA0001</t>
+          <t>TA0043</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Initial Access</t>
+          <t>Reconnaissance</t>
         </is>
       </c>
       <c r="F66" s="11" t="n"/>
       <c r="G66" s="11" t="n"/>
     </row>
-    <row r="67" ht="64" customHeight="1">
+    <row r="67" ht="48" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>F1034</t>
+          <t>F1035</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Interactive Voice Response Mapping</t>
+          <t>Mail Theft</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may interact with interactive voice response systems to understand call flows, authentication mechanisms, or available functions. By mapping IVR systems, fraud actors can identify opportunities for fraud, understand authentication requirements, or develop strategies for social engineering attacks against customer service representatives. IVR discovery may be automated or conducted manually to gather intelligence for fraud operations.</t>
+          <t>Fraud actors may steal physical mail to obtain financial information, payment cards, checks, or identity documents. Mail theft provides access to statements, new payment cards, checks, tax documents, or other financial materials that can be used for fraud. Stolen mail may be intercepted from mailboxes, during postal delivery, or from mail processing facilities.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>TA0043</t>
+          <t>FA0001, TA0043</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Reconnaissance</t>
+          <t>Positioning, Reconnaissance</t>
         </is>
       </c>
       <c r="F67" s="11" t="n"/>
       <c r="G67" s="11" t="n"/>
     </row>
-    <row r="68" ht="48" customHeight="1">
+    <row r="68" ht="80" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>F1035</t>
+          <t>F1036</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Mail Theft</t>
+          <t>New Vendor Setup</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may steal physical mail to obtain financial information, payment cards, checks, or identity documents. Mail theft provides access to statements, new payment cards, checks, tax documents, or other financial materials that can be used for fraud. Stolen mail may be intercepted from mailboxes, during postal delivery, or from mail processing facilities.</t>
+          <t>Fraud actors may pretend to be a new vendor or supplier to trick organizations into directing payments to fraudulent accounts. New vendor setup can be initiated through fake invoices, requests for adding a new payee, banking information change forms, or urgent payment requests that pressure staff to bypass normal verification steps. Once the bogus vendor profile is established in accounts payable or procurement systems, fraud actors can submit additional invoices, alter payment details, or reroute legitimate payments intended for real vendors to accounts they control.</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>FA0001, TA0043</t>
+          <t>FA0001, TA0005</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Positioning, Reconnaissance</t>
+          <t>Positioning, Stealth</t>
         </is>
       </c>
       <c r="F68" s="11" t="n"/>
       <c r="G68" s="11" t="n"/>
     </row>
     <row r="69" ht="80" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>F1036</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>New Vendor Setup</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may pretend to be a new vendor or supplier to trick organizations into directing payments to fraudulent accounts. New vendor setup can be initiated through fake invoices, requests for adding a new payee, banking information change forms, or urgent payment requests that pressure staff to bypass normal verification steps. Once the bogus vendor profile is established in accounts payable or procurement systems, fraud actors can submit additional invoices, alter payment details, or reroute legitimate payments intended for real vendors to accounts they control.</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>FA0001, TA0005</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Positioning, Stealth</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="n"/>
-      <c r="G69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="80" customHeight="1">
-      <c r="A70" s="19" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>F1037</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>NFC Payment</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>Fraud actors exploit NFC (Near Field Communication) payments by using stolen or cloned NFC-enabled cards or mobile devices to make unauthorized transactions. They may intercept or manipulate NFC signals to initiate payments without the legitimate cardholder's knowledge or consent. By leveraging NFC technology, fraud actors can quickly and discreetly conduct fraudulent transactions, often evading traditional security measures such as PIN verification or signature requirements, leading to financial losses for both consumers and businesses.</t>
         </is>
       </c>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr">
         <is>
           <t>TA0002</t>
         </is>
       </c>
-      <c r="E70" s="19" t="inlineStr">
+      <c r="E69" s="19" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="F70" s="24" t="n"/>
-      <c r="G70" s="24" t="n"/>
-    </row>
-    <row r="71" ht="48" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="F69" s="24" t="n"/>
+      <c r="G69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>F1038</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>PAN/CVV Generation</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>Fraud actors use PAN/CVV Generators to create valid credit card numbers (PANs) along with their corresponding Card Verification Values (CVVs), allowing fraud actors to bypass security measures and make unauthorized purchases. By generating PANs and CVVs, fraud actors can create counterfeit credit cards or conduct card-not-present transactions without physically possessing the victim's card.</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F71" s="11" t="n"/>
-      <c r="G71" s="11" t="n"/>
-    </row>
-    <row r="72" ht="80" customHeight="1">
-      <c r="A72" s="19" t="inlineStr">
+      <c r="F70" s="11" t="n"/>
+      <c r="G70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="80" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>F1039</t>
         </is>
       </c>
-      <c r="B72" s="19" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>PaReq Manipulation</t>
         </is>
       </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>Fraud actors exploit Payment Authentication Requests (PaReqs) by manipulating the data within these requests to bypass security measures and gain unauthorized access to sensitive information or transactions. By altering the parameters or contents of PaReqs, they can trick payment systems into approving fraudulent transactions without proper authentication. This manipulation helps fraud actors evade detection by exploiting vulnerabilities in payment processing systems and bypassing security checks designed to prevent unauthorized access or fraudulent transactions.</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>TA0005</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="n"/>
+      <c r="G71" s="24" t="n"/>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>F1040</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>Phone Number Spoofing</t>
+        </is>
+      </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>Fraud actors exploit Payment Authentication Requests (PaReqs) by manipulating the data within these requests to bypass security measures and gain unauthorized access to sensitive information or transactions. By altering the parameters or contents of PaReqs, they can trick payment systems into approving fraudulent transactions without proper authentication. This manipulation helps fraud actors evade detection by exploiting vulnerabilities in payment processing systems and bypassing security checks designed to prevent unauthorized access or fraudulent transactions.</t>
+          <t>Fraud actors may manipulate caller ID information so that outgoing calls appear to originate from a different phone number than the one actually used. This enables them to impersonate trusted organizations or ordinary customers in order to bypass call‑screening controls, establish credibility, and support social engineering or other fraudulent activity.</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>TA0005</t>
+          <t>TA0005, TA0043, TA0001</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Stealth, Reconnaissance, Initial Access</t>
         </is>
       </c>
       <c r="F72" s="24" t="n"/>
       <c r="G72" s="24" t="n"/>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>F1040</t>
-        </is>
-      </c>
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>Phone Number Spoofing</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors may manipulate caller ID information so that outgoing calls appear to originate from a different phone number than the one actually used. This enables them to impersonate trusted organizations or ordinary customers in order to bypass call‑screening controls, establish credibility, and support social engineering or other fraudulent activity.</t>
-        </is>
-      </c>
-      <c r="D73" s="19" t="inlineStr">
+    <row r="73" ht="64" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>F1040.001</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Phone Number Spoofing: Customer Phone Number Spoofing</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may spoof a phone number that appears to belong to a legitimate customer or other ordinary individual when calling financial institutions or other official entities. By presenting themselves as the account holder from a plausible personal number, they attempt to pass identity verification, obtain confidential information about the customer, or convince staff to change account details, reset credentials, or otherwise grant access that facilitates downstream fraud like Impersonate Account Holder.</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>TA0005, TA0043, TA0001</t>
         </is>
       </c>
-      <c r="E73" s="19" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>Stealth, Reconnaissance, Initial Access</t>
         </is>
       </c>
-      <c r="F73" s="24" t="n"/>
-      <c r="G73" s="24" t="n"/>
+      <c r="F73" s="11" t="n"/>
+      <c r="G73" s="11" t="n"/>
     </row>
     <row r="74" ht="64" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>F1040.001</t>
+          <t>F1040.002</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Phone Number Spoofing: Customer Phone Number Spoofing</t>
+          <t>Phone Number Spoofing: Official Phone Number Spoofing</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may spoof a phone number that appears to belong to a legitimate customer or other ordinary individual when calling financial institutions or other official entities. By presenting themselves as the account holder from a plausible personal number, they attempt to pass identity verification, obtain confidential information about the customer, or convince staff to change account details, reset credentials, or otherwise grant access that facilitates downstream fraud like Impersonate Account Holder.</t>
+          <t>Fraud actors may spoof an official phone number associated with a trusted organization, such as a bank, government agency, or law enforcement office, when calling victims. By making the call appear to come from a recognized institution’s published number, they increase the likelihood that targets will trust the caller, disclose sensitive information, or perform high‑risk actions such as approving transactions or granting account access.</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -2742,105 +2742,106 @@
     <row r="75" ht="64" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>F1040.002</t>
+          <t>F1041</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Phone Number Spoofing: Official Phone Number Spoofing</t>
+          <t>PIN-code Peeking</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may spoof an official phone number associated with a trusted organization, such as a bank, government agency, or law enforcement office, when calling victims. By making the call appear to come from a recognized institution’s published number, they increase the likelihood that targets will trust the caller, disclose sensitive information, or perform high‑risk actions such as approving transactions or granting account access.</t>
+          <t>Fraud actors observe or obtain personal identification numbers (PINs). Use of hidden cameras, skimming devices, or other covert methods to capture PINs at ATMs, point-of-sale terminals, or other PIN-entry locations.
+Obtained PIN numbers used with other stolen information to compromise the victim's accounts or conduct fraudulent transactions.</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>TA0005, TA0043, TA0001</t>
+          <t>TA0001, TA0043</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Stealth, Reconnaissance, Initial Access</t>
+          <t>Initial Access, Reconnaissance</t>
         </is>
       </c>
       <c r="F75" s="11" t="n"/>
       <c r="G75" s="11" t="n"/>
     </row>
     <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>F1041</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>PIN-code Peeking</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors observe or obtain personal identification numbers (PINs). Use of hidden cameras, skimming devices, or other covert methods to capture PINs at ATMs, point-of-sale terminals, or other PIN-entry locations.
-Obtained PIN numbers used with other stolen information to compromise the victim's accounts or conduct fraudulent transactions.</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>TA0001, TA0043</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>Initial Access, Reconnaissance</t>
-        </is>
-      </c>
-      <c r="F76" s="11" t="n"/>
-      <c r="G76" s="11" t="n"/>
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>F1042</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>Reactivate Account</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>Fraud actors target inactive bank accounts because they are less likely to be monitored closely by the account holder or financial institution. They may attempt to reactivate the bank account through social engineering or by exploiting loopholes in the bank's security procedures. Once reactivated, they can use the account to launder money, deposit counterfeit checks, or engage in other fraudulent activities, taking advantage of the perceived lack of scrutiny on inactive accounts.</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>FA0001, TA0001</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>Positioning, Initial Access</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="n"/>
+      <c r="G76" s="24" t="n"/>
     </row>
     <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>F1042</t>
-        </is>
-      </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>Reactivate Account</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors target inactive bank accounts because they are less likely to be monitored closely by the account holder or financial institution. They may attempt to reactivate the bank account through social engineering or by exploiting loopholes in the bank's security procedures. Once reactivated, they can use the account to launder money, deposit counterfeit checks, or engage in other fraudulent activities, taking advantage of the perceived lack of scrutiny on inactive accounts.</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>FA0001, TA0001</t>
-        </is>
-      </c>
-      <c r="E77" s="19" t="inlineStr">
-        <is>
-          <t>Positioning, Initial Access</t>
-        </is>
-      </c>
-      <c r="F77" s="24" t="n"/>
-      <c r="G77" s="24" t="n"/>
-    </row>
-    <row r="78" ht="64" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>F1043</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Reversal of Transaction</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors exploit the Reversal of Operation by initially conducting a legitimate transaction, such as purchasing goods or services. After the transaction is complete and the funds have been transferred, they then reverse the transaction, claiming it was unauthorized or fraudulent. This technique may allow them to obtain the goods or services without actually paying for them, effectively evading detection and potentially causing financial loss to the legitimate party involved.</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>TA0002</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="n"/>
+      <c r="G77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="128" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>F1043</t>
+          <t>F1044</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Reversal of Transaction</t>
+          <t>Scheduled Transfer</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors exploit the Reversal of Operation by initially conducting a legitimate transaction, such as purchasing goods or services. After the transaction is complete and the funds have been transferred, they then reverse the transaction, claiming it was unauthorized or fraudulent. This technique may allow them to obtain the goods or services without actually paying for them, effectively evading detection and potentially causing financial loss to the legitimate party involved.</t>
+          <t>Fraud actors use scheduled transfers to systematically move funds out of compromised accounts at predefined intervals. By creating or hijacking recurring payment instructions within online banking or payment services, they can quietly redirect money to accounts they control or to intermediaries that help conceal the origin of the funds.
+Fraud actors may gain access to online banking or payment service accounts and configure new standing orders or modify existing ones to send funds to external destinations. These transfers are typically timed and sized to resemble normal business activity, helping them evade detection while routing money through shell entities, mule accounts, or cryptocurrency services as part of the laundering process.</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -2856,139 +2857,142 @@
       <c r="F78" s="11" t="n"/>
       <c r="G78" s="11" t="n"/>
     </row>
-    <row r="79" ht="128" customHeight="1">
+    <row r="79" ht="80" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>F1044</t>
+          <t>F1045</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Scheduled Transfer</t>
+          <t>Structuring</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors use scheduled transfers to systematically move funds out of compromised accounts at predefined intervals. By creating or hijacking recurring payment instructions within online banking or payment services, they can quietly redirect money to accounts they control or to intermediaries that help conceal the origin of the funds.
-Fraud actors may gain access to online banking or payment service accounts and configure new standing orders or modify existing ones to send funds to external destinations. These transfers are typically timed and sized to resemble normal business activity, helping them evade detection while routing money through shell entities, mule accounts, or cryptocurrency services as part of the laundering process.</t>
+          <t>Fraud actors may structure transactions or account activity by breaking up large movements of funds, spreading activity across multiple accounts, or using different locations and channels to avoid triggering fraud controls and regulatory reporting thresholds. By parcelling deposits, withdrawals, or transfers into smaller amounts that fall below Currency Transaction Report (CTR) or Suspicious Activity Report (SAR) triggers, or by distributing activity over time and across institutions, they aim to keep illicit flows appearing routine and prevent automated systems or investigators from detecting the underlying money laundering or fraud.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>TA0002</t>
+          <t>TA0005</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Stealth</t>
         </is>
       </c>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="11" t="n"/>
     </row>
-    <row r="80" ht="80" customHeight="1">
+    <row r="80" ht="96" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>F1045</t>
+          <t>F1046</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Structuring</t>
+          <t>Test Payment Thresholds</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may structure transactions or account activity by breaking up large movements of funds, spreading activity across multiple accounts, or using different locations and channels to avoid triggering fraud controls and regulatory reporting thresholds. By parcelling deposits, withdrawals, or transfers into smaller amounts that fall below Currency Transaction Report (CTR) or Suspicious Activity Report (SAR) triggers, or by distributing activity over time and across institutions, they aim to keep illicit flows appearing routine and prevent automated systems or investigators from detecting the underlying money laundering or fraud.</t>
+          <t>Fraud actors may perform small, low‑value “test” transactions to verify that stolen or compromised payment instruments can be successfully used before attempting larger fraud. In these tests, they confirm details such as whether the card or account is open, has not been blocked, passes authorization checks (for example, AVS/CVV or 3‑D Secure), and can complete online or card‑not‑present purchases without triggering strong controls. Successful tests indicate that a card or account is likely to support higher‑value charges or cash‑out attempts, allowing fraud actors to prioritize the most viable instruments for large‑scale fraudulent transactions or broader card‑testing campaigns.</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>TA0005</t>
+          <t>FA0001</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="F80" s="11" t="n"/>
       <c r="G80" s="11" t="n"/>
     </row>
-    <row r="81" ht="96" customHeight="1">
+    <row r="81" ht="64" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>F1046</t>
+          <t>F1047</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Test Payment Thresholds</t>
+          <t>Transfer of Funds</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may perform small, low‑value “test” transactions to verify that stolen or compromised payment instruments can be successfully used before attempting larger fraud. In these tests, they confirm details such as whether the card or account is open, has not been blocked, passes authorization checks (for example, AVS/CVV or 3‑D Secure), and can complete online or card‑not‑present purchases without triggering strong controls. Successful tests indicate that a card or account is likely to support higher‑value charges or cash‑out attempts, allowing fraud actors to prioritize the most viable instruments for large‑scale fraudulent transactions or broader card‑testing campaigns.</t>
+          <t>Fraud actors may cause funds to be transferred from a victim or compromised account to an account, wallet, merchant, or payment destination they control or can access through an intermediary. Transfers may use wire, automated clearing house, regional payment rail, peer-to-peer, card, or other electronic mechanisms. The transfer may be initiated without the account holder's authorization or may be executed by a victim who has been deceived, coerced, or impersonated.</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>FA0001</t>
+          <t>FA0002</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Monetization</t>
         </is>
       </c>
       <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
+      <c r="G81" s="11" t="n">
+        <v>46255.5</v>
+      </c>
     </row>
     <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>F1047</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Transfer of Funds</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may cause funds to be transferred from a victim or compromised account to an account, wallet, merchant, or payment destination they control or can access through an intermediary. Transfers may use wire, automated clearing house, regional payment rail, peer-to-peer, card, or other electronic mechanisms. The transfer may be initiated without the account holder's authorization or may be executed by a victim who has been deceived, coerced, or impersonated.</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>F1047.001</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>Transfer of Funds: Victim-Authorized Transfer</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Fraud actors may manipulate a victim into voluntarily authorizing and executing a transfer to an account or payment destination controlled by the fraud actor or an intermediary. The victim uses legitimate credentials and normal payment workflows, often in response to impersonation, coercion, investment, romance, or support pretexts. Because the transaction is authenticated by the account holder, it may appear legitimate to financial controls despite being induced through deception. This activity is also referred to as first-party fraud.</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
         <is>
           <t>FA0002</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E82" s="21" t="inlineStr">
         <is>
           <t>Monetization</t>
         </is>
       </c>
-      <c r="F82" s="11" t="n"/>
-      <c r="G82" s="11" t="n">
+      <c r="F82" s="23" t="n">
         <v>46255.5</v>
+      </c>
+      <c r="G82" s="30" t="n">
+        <v>46294.5</v>
       </c>
     </row>
     <row r="83" ht="64" customHeight="1">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>F1047.001</t>
+          <t>F1047.002</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>Transfer of Funds: Victim-Authorized Transfer</t>
-        </is>
-      </c>
-      <c r="C83" s="28" t="inlineStr">
-        <is>
-          <t>Fraud actors may manipulate a victim into voluntarily authorizing and executing a transfer to an account or payment destination controlled by the fraud actor or an intermediary. The victim uses legitimate credentials and normal payment workflows, often in response to impersonation, coercion, investment, romance, or support pretexts. Because the transaction is authenticated by the account holder, it may appear legitimate to financial controls despite being induced through deception. This activity is also referred to as first-party fraud.</t>
+          <t>Transfer of Funds: Unauthorized Transfer</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>Fraud actors may initiate an unauthorized transfer from a compromised account without the legitimate account holder's approval. This may include wire transfers, automated clearing house transfers, peer-to-peer payments, or other electronic payment mechanisms initiated with stolen credentials, compromised sessions, abused account access, or manipulated payment instructions. Fraud actors may direct the funds to accounts, wallets, merchants, or intermediaries they control. This activity is also referred to as third-party fraud.</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
@@ -3008,93 +3012,93 @@
         <v>46294.5</v>
       </c>
     </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>F1047.002</t>
-        </is>
-      </c>
-      <c r="B84" s="18" t="inlineStr">
-        <is>
-          <t>Transfer of Funds: Unauthorized Transfer</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="inlineStr">
-        <is>
-          <t>Fraud actors may initiate an unauthorized transfer from a compromised account without the legitimate account holder's approval. This may include wire transfers, automated clearing house transfers, peer-to-peer payments, or other electronic payment mechanisms initiated with stolen credentials, compromised sessions, abused account access, or manipulated payment instructions. Fraud actors may direct the funds to accounts, wallets, merchants, or intermediaries they control. This activity is also referred to as third-party fraud.</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>FA0002</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>Monetization</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="n">
-        <v>46255.5</v>
-      </c>
-      <c r="G84" s="30" t="n">
-        <v>46294.5</v>
-      </c>
-    </row>
-    <row r="85" ht="192" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="84" ht="192" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>F1048</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>Use Virtual Cards</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>Fraud actors use virtual cards to facilitate online fraud because they provide flexibility, anonymity, and rapid issuance for card‑not‑present transactions. Virtual cards are often obtained with weaker identity verification or sourced from compromised accounts, making them attractive instruments for testing stolen card data, funding mule accounts, or executing rapid series of purchases and refunds. Their disposability allows fraud actors to run multiple transactions, dispute or reverse charges, and then discard the card, reducing the risk that a single compromised instrument links together the broader scheme.
 Virtual cards are frequently employed in promotion abuse, synthetic identity fraud, and account takeover scenarios, for example, to cash out loyalty points, rotate through trial or subscription offers, or route payments through intermediary wallets and marketplaces. They can also be used to create complex transaction chains across merchants and jurisdictions, complicating efforts to tie specific fraudulent purchases back to the originating compromised identity or account. This flexibility makes virtual cards a convenient tool for scaling and obscuring a wide range of digital fraud schemes, even when they are not explicitly part of a formal money‑laundering process.</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>TA0005</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>Stealth</t>
         </is>
       </c>
-      <c r="F85" s="11" t="n"/>
-      <c r="G85" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>F1049</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>Use Money Mule</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>Fraud actors may use a money mule or mule-controlled account, card, wallet, or payment instrument to receive, hold, transfer, withdraw, purchase, or otherwise move fraud proceeds. Mules may act knowingly or be deceived through employment, romance, investment, or other pretexts. By placing an intermediary between the victim and the fraud actor, mule activity can position funds for further movement while obscuring the fraud actor's identity, location, and control of the proceeds.</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>FA0001, TA0005</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>Positioning, Stealth</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="n">
+        <v>46255.5</v>
+      </c>
+      <c r="G85" s="23" t="n">
+        <v>46255.5</v>
+      </c>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>F1049</t>
+          <t>F1050</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>Use Money Mule</t>
+          <t>Operate Fraudulent Call Centers</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>Fraud actors may use a money mule or mule-controlled account, card, wallet, or payment instrument to receive, hold, transfer, withdraw, purchase, or otherwise move fraud proceeds. Mules may act knowingly or be deceived through employment, romance, investment, or other pretexts. By placing an intermediary between the victim and the fraud actor, mule activity can position funds for further movement while obscuring the fraud actor's identity, location, and control of the proceeds.</t>
+          <t>Fraud actors may establish or operate coordinated call-center infrastructure to conduct fraud at scale. They may acquire phone systems, spoofed numbers, scripts, customer data, and teams of callers who impersonate trusted organizations or individuals. Centralized operations allow repeated voice phishing, account-recovery abuse, collection of credentials or one-time codes, and manipulation of victims into authorizing transactions.</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>FA0001, TA0005</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="inlineStr">
-        <is>
-          <t>Positioning, Stealth</t>
+          <t>TA0042, TA0001</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>Resource Development, Initial Access</t>
         </is>
       </c>
       <c r="F86" s="23" t="n">
@@ -3104,97 +3108,97 @@
         <v>46255.5</v>
       </c>
     </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>F1050</t>
-        </is>
-      </c>
-      <c r="B87" s="18" t="inlineStr">
-        <is>
-          <t>Operate Fraudulent Call Centers</t>
-        </is>
-      </c>
-      <c r="C87" s="21" t="inlineStr">
-        <is>
-          <t>Fraud actors may establish or operate coordinated call-center infrastructure to conduct fraud at scale. They may acquire phone systems, spoofed numbers, scripts, customer data, and teams of callers who impersonate trusted organizations or individuals. Centralized operations allow repeated voice phishing, account-recovery abuse, collection of credentials or one-time codes, and manipulation of victims into authorizing transactions.</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>TA0042, TA0001</t>
-        </is>
-      </c>
-      <c r="E87" s="28" t="inlineStr">
-        <is>
-          <t>Resource Development, Initial Access</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="n">
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>F1053</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Compromise Point-of-Sale Systems</t>
+        </is>
+      </c>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>Fraud actors may compromise point-of-sale terminals to capture payment data, manipulate transactions, or obtain unauthorized funds. Compromise may involve exploiting software vulnerabilities, installing malware, altering terminal configuration, connecting unauthorized hardware, or abusing remote administration access. Fraud actors may use the compromised system to collect card data and PINs, redirect payments, issue fraudulent refunds, or conceal unauthorized transactions.</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>TA0001, TA0002</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>Initial Access, Execution</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n">
         <v>46255.5</v>
       </c>
-      <c r="G87" s="23" t="n">
+      <c r="G87" s="17" t="n">
         <v>46255.5</v>
       </c>
     </row>
-    <row r="88" ht="48" customHeight="1">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>F1053</t>
-        </is>
-      </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>Compromise Point-of-Sale Systems</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="inlineStr">
-        <is>
-          <t>Fraud actors may compromise point-of-sale terminals to capture payment data, manipulate transactions, or obtain unauthorized funds. Compromise may involve exploiting software vulnerabilities, installing malware, altering terminal configuration, connecting unauthorized hardware, or abusing remote administration access. Fraud actors may use the compromised system to collect card data and PINs, redirect payments, issue fraudulent refunds, or conceal unauthorized transactions.</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>TA0001, TA0002</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>Initial Access, Execution</t>
-        </is>
-      </c>
-      <c r="F88" s="17" t="n">
-        <v>46255.5</v>
-      </c>
-      <c r="G88" s="17" t="n">
-        <v>46255.5</v>
-      </c>
-    </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="18" t="inlineStr">
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
         <is>
           <t>F1054</t>
         </is>
       </c>
-      <c r="B89" s="18" t="inlineStr">
+      <c r="B88" s="18" t="inlineStr">
         <is>
           <t>Clone Victim Device</t>
         </is>
       </c>
-      <c r="C89" s="28" t="inlineStr">
+      <c r="C88" s="28" t="inlineStr">
         <is>
           <t>Fraud actors may clone a cellular phone by reprogramming another handset to transmit the subscriber identifiers assigned to a legitimate device. In legacy cellular systems, these identifiers may include the electronic serial number (ESN), mobile identification number (MIN), and system identification number (SID). Fraud actors may obtain valid identifier combinations by unlawfully monitoring radio transmissions or through other compromised sources.
 When the legitimate and cloned phones transmit the same identifiers, the cellular network may be unable to distinguish between them. This may allow fraud actors to obtain unauthorized telecommunications access, place calls, or incur charges that are billed to the legitimate subscriber. This technique is specific to cloning a cellular device’s network identity and is distinct from Device Fingerprint Spoofing, which manipulates device characteristics evaluated by fraud-detection systems.</t>
         </is>
       </c>
+      <c r="D88" s="21" t="inlineStr">
+        <is>
+          <t>TA0005, TA0001</t>
+        </is>
+      </c>
+      <c r="E88" s="21" t="inlineStr">
+        <is>
+          <t>Stealth, Initial Access</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="n">
+        <v>46255.5</v>
+      </c>
+      <c r="G88" s="23" t="n">
+        <v>46255.5</v>
+      </c>
+    </row>
+    <row r="89" ht="144" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>F1055</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Search Dark Web</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>Fraud actors may search dark-web marketplaces, access-controlled forums, leak sites, criminal communities, or other non-public online sources for information that can support fraud. They may look for exposed credentials, payment data, customer records, organization details, vulnerabilities, access offers, or operational guidance. Information gathered from dark-web sources may be used to identify targets, select an initial access vector, purchase supporting resources, or tailor follow-on social-engineering and account-takeover activity.</t>
+        </is>
+      </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>TA0005, TA0001</t>
+          <t>TA0043</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>Stealth, Initial Access</t>
+          <t>Reconnaissance</t>
         </is>
       </c>
       <c r="F89" s="23" t="n">
@@ -3204,30 +3208,30 @@
         <v>46255.5</v>
       </c>
     </row>
-    <row r="90" ht="144" customHeight="1">
+    <row r="90" ht="80" customHeight="1">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>F1055</t>
+          <t>F1056</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
         <is>
-          <t>Search Dark Web</t>
-        </is>
-      </c>
-      <c r="C90" s="21" t="inlineStr">
-        <is>
-          <t>Fraud actors may search dark-web marketplaces, access-controlled forums, leak sites, criminal communities, or other non-public online sources for information that can support fraud. They may look for exposed credentials, payment data, customer records, organization details, vulnerabilities, access offers, or operational guidance. Information gathered from dark-web sources may be used to identify targets, select an initial access vector, purchase supporting resources, or tailor follow-on social-engineering and account-takeover activity.</t>
+          <t>Impersonate Trusted Person</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>Fraud actors may impersonate a person that a victim knows or trusts, such as a co-worker, family member, or business partner. They may use email, messaging, phone calls, social media, or other communication channels to make requests appear legitimate. By exploiting an existing relationship, fraud actors may convince victims to disclose information, change payment details, approve access, or perform fraudulent transactions.</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>TA0043</t>
+          <t>TA0001, TA0005</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>Reconnaissance</t>
+          <t>Initial Access, Stealth</t>
         </is>
       </c>
       <c r="F90" s="23" t="n">
@@ -3237,30 +3241,30 @@
         <v>46255.5</v>
       </c>
     </row>
-    <row r="91" ht="80" customHeight="1">
+    <row r="91" ht="64" customHeight="1">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>F1056</t>
+          <t>F1057</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
         <is>
-          <t>Impersonate Trusted Person</t>
+          <t>Payment via Gift Card</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>Fraud actors may impersonate a person that a victim knows or trusts, such as a co-worker, family member, or business partner. They may use email, messaging, phone calls, social media, or other communication channels to make requests appear legitimate. By exploiting an existing relationship, fraud actors may convince victims to disclose information, change payment details, approve access, or perform fraudulent transactions.</t>
-        </is>
-      </c>
-      <c r="D91" s="21" t="inlineStr">
-        <is>
-          <t>TA0001, TA0005</t>
-        </is>
-      </c>
-      <c r="E91" s="21" t="inlineStr">
-        <is>
-          <t>Initial Access, Stealth</t>
+          <t>Fraud actors may obtain or direct payment through physical or digital gift cards to receive, transfer, or launder money. They may use stolen funds to purchase gift cards, coerce victims to provide gift-card numbers or redemption codes, or move value through gift-card exchanges and resale markets. Gift cards can provide rapid settlement, broad availability, and reduced linkage to traditional bank accounts, allowing fraud actors to spend or resell the value while obscuring the original source of funds.</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t>FA0002</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="inlineStr">
+        <is>
+          <t>Monetization</t>
         </is>
       </c>
       <c r="F91" s="23" t="n">
@@ -3273,27 +3277,27 @@
     <row r="92" ht="64" customHeight="1">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>F1057</t>
+          <t>F1058</t>
         </is>
       </c>
       <c r="B92" s="18" t="inlineStr">
         <is>
-          <t>Payment via Gift Card</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="inlineStr">
-        <is>
-          <t>Fraud actors may obtain or direct payment through physical or digital gift cards to receive, transfer, or launder money. They may use stolen funds to purchase gift cards, coerce victims to provide gift-card numbers or redemption codes, or move value through gift-card exchanges and resale markets. Gift cards can provide rapid settlement, broad availability, and reduced linkage to traditional bank accounts, allowing fraud actors to spend or resell the value while obscuring the original source of funds.</t>
-        </is>
-      </c>
-      <c r="D92" s="28" t="inlineStr">
-        <is>
-          <t>FA0002</t>
-        </is>
-      </c>
-      <c r="E92" s="28" t="inlineStr">
-        <is>
-          <t>Monetization</t>
+          <t>Train AI Model</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="inlineStr">
+        <is>
+          <t>Fraud actors may train, fine-tune, prompt, or otherwise configure artificial intelligence models to support fraud operations. They may use stolen data, synthetic identities, impersonation scripts, target-specific information, or prior victim interactions to improve model outputs. Trained models may generate convincing messages and media, automate interactive conversations, adapt social-engineering pretexts, or scale fraud activity across many targets and communication channels.</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>TA0042</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>Resource Development</t>
         </is>
       </c>
       <c r="F92" s="23" t="n">
@@ -3306,27 +3310,27 @@
     <row r="93" ht="64" customHeight="1">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>F1058</t>
+          <t>F1059</t>
         </is>
       </c>
       <c r="B93" s="18" t="inlineStr">
         <is>
-          <t>Train AI Model</t>
+          <t>Coercion</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>Fraud actors may train, fine-tune, prompt, or otherwise configure artificial intelligence models to support fraud operations. They may use stolen data, synthetic identities, impersonation scripts, target-specific information, or prior victim interactions to improve model outputs. Trained models may generate convincing messages and media, automate interactive conversations, adapt social-engineering pretexts, or scale fraud activity across many targets and communication channels.</t>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>TA0042</t>
-        </is>
-      </c>
-      <c r="E93" s="21" t="inlineStr">
-        <is>
-          <t>Resource Development</t>
+          <t>Fraud actors may pressure, threaten, manipulate, or otherwise coerce a victim into taking an action that supports fraud. They may create urgency, claim that funds or accounts are at risk, invoke authority, threaten financial or personal consequences, or maintain prolonged psychological pressure. Coercion may position the victim to disclose information, change account settings, grant access, or execute transactions, and may continue while the fraudulent action is performed.</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="inlineStr">
+        <is>
+          <t>FA0001, TA0002, TA0001</t>
+        </is>
+      </c>
+      <c r="E93" s="28" t="inlineStr">
+        <is>
+          <t>Positioning, Execution, Initial Access</t>
         </is>
       </c>
       <c r="F93" s="23" t="n">
@@ -3336,53 +3340,53 @@
         <v>46255.5</v>
       </c>
     </row>
-    <row r="94" ht="64" customHeight="1">
+    <row r="94" ht="80" customHeight="1">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>F1059</t>
+          <t>T1056</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
         <is>
-          <t>Coercion</t>
+          <t>Input Capture</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Fraud actors may pressure, threaten, manipulate, or otherwise coerce a victim into taking an action that supports fraud. They may create urgency, claim that funds or accounts are at risk, invoke authority, threaten financial or personal consequences, or maintain prolonged psychological pressure. Coercion may position the victim to disclose information, change account settings, grant access, or execute transactions, and may continue while the fraudulent action is performed.</t>
+          <t>Fraud actors may use methods of capturing user input to obtain credentials, payment information, authentication codes, or other data that can support fraud. During normal system use, users provide sensitive information to login pages, transaction forms, payment applications, system dialogs, and communication tools. Input capture mechanisms may operate transparently, such as keylogging or API hooking, or may deceive users into entering data into a fraudulent interface. Fraud actors may use captured information to conduct account takeover, bypass authentication, initiate unauthorized transactions, or develop targeting for subsequent fraud activity.</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t>FA0001, TA0002, TA0001</t>
+          <t>TA0043</t>
         </is>
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
-          <t>Positioning, Execution, Initial Access</t>
+          <t>Reconnaissance</t>
         </is>
       </c>
       <c r="F94" s="23" t="n">
-        <v>46255.5</v>
+        <v>46294.5</v>
       </c>
       <c r="G94" s="23" t="n">
-        <v>46255.5</v>
+        <v>46294.5</v>
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>T1056</t>
+          <t>T1056.001</t>
         </is>
       </c>
       <c r="B95" s="18" t="inlineStr">
         <is>
-          <t>Input Capture</t>
+          <t>Input Capture: Keylogging</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>Fraud actors may use methods of capturing user input to obtain credentials, payment information, authentication codes, or other data that can support fraud. During normal system use, users provide sensitive information to login pages, transaction forms, payment applications, system dialogs, and communication tools. Input capture mechanisms may operate transparently, such as keylogging or API hooking, or may deceive users into entering data into a fraudulent interface. Fraud actors may use captured information to conduct account takeover, bypass authentication, initiate unauthorized transactions, or develop targeting for subsequent fraud activity.</t>
+          <t>Fraud actors may log user keystrokes to intercept credentials as the user types them. Keylogging may be used when other credential-acquisition methods are ineffective and may require monitoring a system until credentials or payment data are entered. Fraud actors may capture keystrokes through API hooks, raw hardware buffers, registry changes, custom drivers, or modified system components. In fraud operations, captured credentials, one-time codes, card data, or transaction details may support account takeover, authentication bypass, or unauthorized payments.</t>
         </is>
       </c>
       <c r="D95" s="28" t="inlineStr">
@@ -3396,153 +3400,150 @@
         </is>
       </c>
       <c r="F95" s="23" t="n">
-        <v>46294.5</v>
+        <v>46255.5</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>46294.5</v>
-      </c>
-    </row>
-    <row r="96" ht="80" customHeight="1">
-      <c r="A96" s="18" t="inlineStr">
-        <is>
-          <t>T1056.001</t>
-        </is>
-      </c>
-      <c r="B96" s="18" t="inlineStr">
-        <is>
-          <t>Input Capture: Keylogging</t>
-        </is>
-      </c>
-      <c r="C96" s="21" t="inlineStr">
-        <is>
-          <t>Fraud actors may log user keystrokes to intercept credentials as the user types them. Keylogging may be used when other credential-acquisition methods are ineffective and may require monitoring a system until credentials or payment data are entered. Fraud actors may capture keystrokes through API hooks, raw hardware buffers, registry changes, custom drivers, or modified system components. In fraud operations, captured credentials, one-time codes, card data, or transaction details may support account takeover, authentication bypass, or unauthorized payments.</t>
-        </is>
-      </c>
-      <c r="D96" s="28" t="inlineStr">
-        <is>
-          <t>TA0043</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="inlineStr">
-        <is>
-          <t>Reconnaissance</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="n">
         <v>46255.5</v>
       </c>
-      <c r="G96" s="23" t="n">
-        <v>46255.5</v>
-      </c>
-    </row>
-    <row r="97" ht="144" customHeight="1">
-      <c r="A97" s="19" t="inlineStr">
+    </row>
+    <row r="96" ht="144" customHeight="1">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>T1070</t>
         </is>
       </c>
-      <c r="B97" s="19" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>Indicator Removal</t>
         </is>
       </c>
-      <c r="C97" s="19" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may delete or modify artifacts generated within systems to remove evidence of their presence or hinder defenses. Various artifacts may be created by a fraud actor or something that can be attributed to afraud actor’s actions. Typically these artifacts are used as defensive indicators related to monitored events, such as strings from downloaded files, logs that are generated from user actions, and other data analyzed by defenders. Location, format, and type of artifact (such as command or login history) are often specific to each platform.
 Removal of these indicators may interfere with event collection, reporting, or other processes used to detect intrusion activity. This may compromise the integrity of security solutions by causing notable events to go unreported. This activity may also impede forensic analysis and incident response, due to lack of sufficient data to determine what occurred.</t>
         </is>
       </c>
-      <c r="D97" s="19" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>TA0005</t>
         </is>
       </c>
-      <c r="E97" s="19" t="inlineStr">
+      <c r="E96" s="19" t="inlineStr">
         <is>
           <t>Stealth</t>
         </is>
       </c>
-      <c r="F97" s="24" t="n"/>
-      <c r="G97" s="24" t="n"/>
-    </row>
-    <row r="98" ht="192" customHeight="1">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="F96" s="24" t="n"/>
+      <c r="G96" s="24" t="n"/>
+    </row>
+    <row r="97" ht="192" customHeight="1">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>T1110</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>Brute Force</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may use brute force techniques to gain access to accounts when passwords are unknown or when password hashes are obtained. Without knowledge of the password for an account or set of accounts, a fraud actor may systematically guess the password using a repetitive or iterative mechanism. Brute forcing passwords can take place via interaction with a service that will check the validity of those credentials or offline against previously acquired credential data, such as password hashes.
 Brute forcing credentials may take place at various points during a breach. For example, fraud actors may attempt to brute force access to Valid Accounts within a victim environment leveraging knowledge gathered from other post-compromise behaviors such as OS Credential Dumping, Account Discovery, or Password Policy Discovery. Fraud actors may also combine brute forcing activity with behaviors such as External Remote Services as part of Initial Access.
 If a fraud actor guesses the correct password but fails to login to a compromised account due to location-based conditional access policies, they may change their infrastructure until they match the victim’s location and therefore bypass those policies.</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F98" s="11" t="n"/>
-      <c r="G98" s="11" t="n"/>
-    </row>
-    <row r="99" ht="128" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="128" customHeight="1">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>T1110.001</t>
         </is>
       </c>
-      <c r="B99" s="19" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>Brute Force: Password Guessing</t>
         </is>
       </c>
-      <c r="C99" s="19" t="inlineStr">
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>Fraud actors with no prior knowledge of legitimate credentials within the system or environment may guess passwords to attempt access to accounts. Without knowledge of the password for an account, a fraud actor may opt to systematically guess the password using a repetitive or iterative mechanism. A fraud actor may guess login credentials without prior knowledge of system or environment passwords during an operation by using a list of common passwords. Password guessing may or may not take into account the target's policies on password complexity or use policies that may lock accounts out after a number of failed attempts.
 Guessing passwords can be a risky option because it could cause numerous authentication failures and account lockouts, depending on the organization's login failure policies.</t>
         </is>
       </c>
-      <c r="D99" s="19" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E99" s="19" t="inlineStr">
+      <c r="E98" s="19" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F99" s="24" t="n"/>
-      <c r="G99" s="24" t="n"/>
-    </row>
-    <row r="100" ht="144" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="F98" s="24" t="n"/>
+      <c r="G98" s="24" t="n"/>
+    </row>
+    <row r="99" ht="144" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>T1110.002</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>Brute Force: Password Cracking</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may use password cracking to attempt to recover usable credentials, such as plaintext passwords, when credential material such as password hashes are obtained. OS Credential Dumping can be used to obtain password hashes, this may only get a fraud actor so far when Pass the Hash is not an option. Further, fraud actors may leverage Data from Configuration Repository in order to obtain hashed credentials for network devices.
 Techniques to systematically guess the passwords used to compute hashes are available, or the fraud actor may use a pre-computed rainbow table to crack hashes. Cracking hashes is usually done on fraudster-controlled systems outside of the target network. The resulting plaintext password resulting from a successfully cracked hash may be used to log into systems, resources, and services in which the account has access.</t>
         </is>
       </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>TA0001</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Initial Access</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="11" t="n"/>
+    </row>
+    <row r="100" ht="128" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>T1110.003</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Brute Force: Password Spraying</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may use a single or small list of commonly used passwords against many different accounts to attempt to acquire valid account credentials. Password spraying uses one password (e.g. 'Password01'), or a small list of commonly used passwords, that may match the complexity policy of the domain. Logins are attempted with that password against many different accounts on a network to avoid account lockouts that would normally occur when brute forcing a single account with many passwords.
+In order to avoid detection thresholds, fraud actors may deliberately throttle password spraying attempts to avoid triggering security alerting. Additionally, fraud actors may leverage LDAP and Kerberos authentication attempts, which are less likely to trigger high-visibility events such as Windows "logon failure" event ID 4625 that is commonly triggered by failed SMB connection attempts.</t>
+        </is>
+      </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
           <t>TA0001</t>
@@ -3556,21 +3557,21 @@
       <c r="F100" s="11" t="n"/>
       <c r="G100" s="11" t="n"/>
     </row>
-    <row r="101" ht="128" customHeight="1">
+    <row r="101" ht="112" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>T1110.003</t>
+          <t>T1110.004</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Brute Force: Password Spraying</t>
+          <t>Brute Force:  Credential Stuffing</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may use a single or small list of commonly used passwords against many different accounts to attempt to acquire valid account credentials. Password spraying uses one password (e.g. 'Password01'), or a small list of commonly used passwords, that may match the complexity policy of the domain. Logins are attempted with that password against many different accounts on a network to avoid account lockouts that would normally occur when brute forcing a single account with many passwords.
-In order to avoid detection thresholds, fraud actors may deliberately throttle password spraying attempts to avoid triggering security alerting. Additionally, fraud actors may leverage LDAP and Kerberos authentication attempts, which are less likely to trigger high-visibility events such as Windows "logon failure" event ID 4625 that is commonly triggered by failed SMB connection attempts.</t>
+          <t>Fraud actors may use credentials obtained from breach dumps of unrelated accounts to gain access to target accounts through credential overlap. Occasionally, large numbers of username and password pairs are dumped online when a website or service is compromised and the user account credentials accessed. The information may be useful to a fraud actor attempting to compromise accounts by taking advantage of the tendency for users to use the same passwords across personal and business accounts.
+Credential stuffing is a risky option because it could cause numerous authentication failures and account lockouts, depending on the organization's login failure policies.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -3586,137 +3587,107 @@
       <c r="F101" s="11" t="n"/>
       <c r="G101" s="11" t="n"/>
     </row>
-    <row r="102" ht="112" customHeight="1">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>T1110.004</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>Brute Force:  Credential Stuffing</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may use credentials obtained from breach dumps of unrelated accounts to gain access to target accounts through credential overlap. Occasionally, large numbers of username and password pairs are dumped online when a website or service is compromised and the user account credentials accessed. The information may be useful to a fraud actor attempting to compromise accounts by taking advantage of the tendency for users to use the same passwords across personal and business accounts.
-Credential stuffing is a risky option because it could cause numerous authentication failures and account lockouts, depending on the organization's login failure policies.</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
+    <row r="102" ht="64" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>T1111</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>Multi-Factor Authentication Interception</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Fraud actors may intercept multi-factor authentication credentials or tokens to bypass additional security controls. This may include intercepting SMS messages containing one-time codes, capturing push notification approvals, compromising hardware tokens, or exploiting vulnerabilities in MFA implementations. Successful MFA interception allows fraud actors to complete authentication despite not possessing legitimate MFA credentials.</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F102" s="11" t="n"/>
-      <c r="G102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="64" customHeight="1">
-      <c r="A103" s="14" t="inlineStr">
-        <is>
-          <t>T1111</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>Multi-Factor Authentication Interception</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>Fraud actors may intercept multi-factor authentication credentials or tokens to bypass additional security controls. This may include intercepting SMS messages containing one-time codes, capturing push notification approvals, compromising hardware tokens, or exploiting vulnerabilities in MFA implementations. Successful MFA interception allows fraud actors to complete authentication despite not possessing legitimate MFA credentials.</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>TA0001</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Initial Access</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="n"/>
-      <c r="G103" s="13" t="n"/>
-    </row>
-    <row r="104" ht="48" customHeight="1">
+      <c r="F102" s="13" t="n"/>
+      <c r="G102" s="13" t="n"/>
+    </row>
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>T1113</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Screen Capture</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may attempt to take screen captures of the desktop to gather information over the course of an operation. Screen capturing functionality may be included as a feature of a remote access tool used in post-compromise operations. Taking a screenshot is also typically possible through native utilities or API calls, such as CopyFromScreen, xwd, or screencapture.</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>FA0001</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="11" t="n"/>
+    </row>
+    <row r="104" ht="224" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>T1113</t>
+          <t>T1185</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Screen Capture</t>
+          <t>Browser Session Hijacking</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may attempt to take screen captures of the desktop to gather information over the course of an operation. Screen capturing functionality may be included as a feature of a remote access tool used in post-compromise operations. Taking a screenshot is also typically possible through native utilities or API calls, such as CopyFromScreen, xwd, or screencapture.</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>FA0001</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>Positioning</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="n"/>
-      <c r="G104" s="11" t="n"/>
-    </row>
-    <row r="105" ht="224" customHeight="1">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>T1185</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Browser Session Hijacking</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may take advantage of security vulnerabilities and inherent functionality in browser software to change content, modify user-behaviors, and intercept information as part of various browser session hijacking techniques.
 A specific example is when a fraud actor injects software into a browser that allows them to inherit cookies, HTTP sessions, and SSL client certificates of a user then use the browser as a way to pivot into an authenticated intranet. Executing browser-based behaviors such as pivoting may require specific process permissions, such as SeDebugPrivilege and/or high-integrity/administrator rights
 Another example involves pivoting browser traffic from the fraud actor's browser through the user's browser by setting up a proxy which will redirect web traffic. This does not alter the user's traffic in any way, and the proxy connection can be severed as soon as the browser is closed. The fraud actor assumes the security context of whichever browser process the proxy is injected into. Browsers typically create a new process for each tab that is opened and permissions and certificates are separated accordingly. With these permissions, a fraud actor could potentially browse to any resource on an intranet, such as SharePoint or webmail, that is accessible through the browser and which the browser has sufficient permissions. Browser pivoting may also bypass security provided by 2-factor authentication.</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>TA0001, FA0001</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E104" s="9" t="inlineStr">
         <is>
           <t>Initial Access, Positioning</t>
         </is>
       </c>
-      <c r="F105" s="11" t="n"/>
-      <c r="G105" s="11" t="n"/>
-    </row>
-    <row r="106" ht="208" customHeight="1">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="F104" s="11" t="n"/>
+      <c r="G104" s="11" t="n"/>
+    </row>
+    <row r="105" ht="208" customHeight="1">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>T1189</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>Drive-by Compromise</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may gain access to a system through a user visiting a website over the normal course of browsing. Multiple ways of delivering exploit code to a browser exist (i.e., Drive-by Target), including: 
 - A legitimate website is compromised, allowing fraud actors to inject malicious code
@@ -3727,31 +3698,31 @@
 Often the website used by a fraud actor is one visited by a specific community, such as government, a particular industry, or a particular region, where the goal is to compromise a specific user or set of users based on a shared interest. This kind of targeted campaign is often referred to a strategic web compromise or watering hole attack. There are several known examples of this occurring.</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E105" s="9" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F106" s="11" t="n"/>
-      <c r="G106" s="11" t="n"/>
-    </row>
-    <row r="107" ht="380" customHeight="1">
-      <c r="A107" s="19" t="inlineStr">
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="380" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>T1195</t>
         </is>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>Supply Chain Compromise</t>
         </is>
       </c>
-      <c r="C107" s="19" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may manipulate products or product delivery mechanisms prior to receipt by a final consumer for the purpose of data or system compromise.
 Supply chain compromise can take place at any stage of the supply chain including:
@@ -3768,147 +3739,147 @@
 In some cases, fraud actors may conduct "second-order" supply chain compromises by leveraging the access gained from an initial supply chain compromise to further compromise a software component. This may allow the threat actor to spread to even more victims.</t>
         </is>
       </c>
-      <c r="D107" s="19" t="inlineStr">
+      <c r="D106" s="19" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E107" s="19" t="inlineStr">
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F107" s="24" t="n"/>
-      <c r="G107" s="24" t="n"/>
-    </row>
-    <row r="108" ht="112" customHeight="1">
+      <c r="F106" s="24" t="n"/>
+      <c r="G106" s="24" t="n"/>
+    </row>
+    <row r="107" ht="112" customHeight="1">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>T1219</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Remote Access Tools</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>A fraud actor may use legitimate remote access tools to establish an interactive command and control channel within a network. Remote access tools create a session between two trusted hosts through a graphical interface, a command line interaction, a protocol tunnel via development or management software, or hardware-level access such as KVM (Keyboard, Video, Mouse) over IP solutions. Desktop support software (usually graphical interface) and remote management software (typically command line interface) allow a user to control a computer remotely as if they are a local user inheriting the user or software permissions. This software is commonly used for troubleshooting, software installation, and system management. Fraud actors may similarly abuse response features included in EDR and other defensive tools that enable remote access</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>FA0001</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="n"/>
+      <c r="G107" s="11" t="n"/>
+    </row>
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>T1219</t>
+          <t>T1451</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Remote Access Tools</t>
+          <t>SIM Card Swap</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>A fraud actor may use legitimate remote access tools to establish an interactive command and control channel within a network. Remote access tools create a session between two trusted hosts through a graphical interface, a command line interaction, a protocol tunnel via development or management software, or hardware-level access such as KVM (Keyboard, Video, Mouse) over IP solutions. Desktop support software (usually graphical interface) and remote management software (typically command line interface) allow a user to control a computer remotely as if they are a local user inheriting the user or software permissions. This software is commonly used for troubleshooting, software installation, and system management. Fraud actors may similarly abuse response features included in EDR and other defensive tools that enable remote access</t>
+          <t>Unauthorized SIM changes including swapping to a new SIM card within the same carrier or porting the phone number to a new SIM card at a new carrier. This results in voice and SMS communications being redirected to the threat-actor.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>FA0001</t>
+          <t>TA0001</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Initial Access</t>
         </is>
       </c>
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="11" t="n"/>
     </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>T1451</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>SIM Card Swap</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Unauthorized SIM changes including swapping to a new SIM card within the same carrier or porting the phone number to a new SIM card at a new carrier. This results in voice and SMS communications being redirected to the threat-actor.</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>TA0001</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>Initial Access</t>
-        </is>
-      </c>
-      <c r="F109" s="11" t="n"/>
-      <c r="G109" s="11" t="n"/>
-    </row>
-    <row r="110" ht="80" customHeight="1">
-      <c r="A110" s="19" t="inlineStr">
+    <row r="109" ht="80" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
         <is>
           <t>T1453</t>
         </is>
       </c>
-      <c r="B110" s="19" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>Abuse Accessibility Features</t>
         </is>
       </c>
-      <c r="C110" s="19" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may abuse accessibility features on mobile devices to intercept and manipulate authentication processes. Malicious applications may request accessibility service permissions, enabling them to monitor screen content, intercept authentication prompts, and capture one-time passwords or other multi-factor authentication codes displayed on the device. This technique allows fraud actors to bypass security controls by gaining unauthorized access to sensitive information presented through legitimate authentication interfaces.</t>
         </is>
       </c>
-      <c r="D110" s="19" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>FA0001</t>
         </is>
       </c>
-      <c r="E110" s="19" t="inlineStr">
+      <c r="E109" s="19" t="inlineStr">
         <is>
           <t>Positioning</t>
         </is>
       </c>
-      <c r="F110" s="24" t="n"/>
-      <c r="G110" s="24" t="n"/>
-    </row>
-    <row r="111" ht="64" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="F109" s="24" t="n"/>
+      <c r="G109" s="24" t="n"/>
+    </row>
+    <row r="110" ht="64" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>T1531</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>Account Access Removal</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may remove or alter account access controls after gaining unauthorized access to lock out legitimate account owners. This may include changing login credentials, modifying account recovery information, or manipulating user roles and permissions within enterprise systems. By preventing the legitimate owner from regaining access, fraud actors maintain persistent control over compromised accounts.</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>FA0001</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="E110" s="9" t="inlineStr">
         <is>
           <t>Positioning</t>
         </is>
       </c>
-      <c r="F111" s="11" t="n"/>
-      <c r="G111" s="11" t="n"/>
-    </row>
-    <row r="112" ht="288" customHeight="1">
-      <c r="A112" s="20" t="inlineStr">
+      <c r="F110" s="11" t="n"/>
+      <c r="G110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="288" customHeight="1">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>T1539</t>
         </is>
       </c>
-      <c r="B112" s="20" t="inlineStr">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>Steal Web Session Cookie</t>
         </is>
       </c>
-      <c r="C112" s="22" t="inlineStr">
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>A fraud actor may steal web application or service session cookies and use them to gain access to web applications or Internet services as an authenticated user without needing credentials. Web applications and services often use session cookies as an authentication token after a user has authenticated to a website.
 Cookies are often valid for an extended period of time, even if the web application is not actively used. Cookies can be found on disk, in the process memory of the browser, and in network traffic to remote systems. Additionally, other applications on the targets machine might store sensitive authentication cookies in memory (e.g. apps which authenticate to cloud services). Session cookies can be used to bypasses some multi-factor authentication protocols.
@@ -3917,91 +3888,120 @@
 After a fraud actor acquires a valid cookie, they can then perform a Web Session Cookie technique to login to the corresponding web application.</t>
         </is>
       </c>
-      <c r="D112" s="22" t="inlineStr">
+      <c r="D111" s="22" t="inlineStr">
         <is>
           <t>FA0001, TA0001</t>
         </is>
       </c>
-      <c r="E112" s="22" t="inlineStr">
+      <c r="E111" s="22" t="inlineStr">
         <is>
           <t>Positioning, Initial Access</t>
         </is>
       </c>
-      <c r="F112" s="25" t="n"/>
-      <c r="G112" s="25" t="n"/>
+      <c r="F111" s="25" t="n"/>
+      <c r="G111" s="25" t="n"/>
+    </row>
+    <row r="112" ht="64" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>T1550</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>Use Alternate Authentication Material</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>Fraud actors may use authentication materials other than passwords to gain unauthorized access to accounts or systems. This may include using stolen authentication tokens, session cookies, API keys, or biometric data. Alternate authentication materials may be longer-lived than passwords, may not trigger password-based security controls, or may be easier to steal than passwords in certain scenarios.</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>TA0001</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>Initial Access</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="n"/>
+      <c r="G112" s="24" t="n"/>
     </row>
     <row r="113" ht="64" customHeight="1">
-      <c r="A113" s="19" t="inlineStr">
-        <is>
-          <t>T1550</t>
-        </is>
-      </c>
-      <c r="B113" s="19" t="inlineStr">
-        <is>
-          <t>Use Alternate Authentication Material</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors may use authentication materials other than passwords to gain unauthorized access to accounts or systems. This may include using stolen authentication tokens, session cookies, API keys, or biometric data. Alternate authentication materials may be longer-lived than passwords, may not trigger password-based security controls, or may be easier to steal than passwords in certain scenarios.</t>
-        </is>
-      </c>
-      <c r="D113" s="19" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>T1550.001</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Use Alternate Authentication Material: Application Access Token</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may use stolen application access tokens to authenticate to services without requiring passwords or MFA. Access tokens are often long-lived, may have broad permissions, and may not be protected as carefully as passwords. Stolen tokens can be obtained through malware, phishing, insecure storage, or compromised applications. Using stolen tokens allows fraud actors to bypass password-based authentication controls and may not trigger alerts for unusual login locations.</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E113" s="19" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F113" s="24" t="n"/>
-      <c r="G113" s="24" t="n"/>
+      <c r="F113" s="11" t="n"/>
+      <c r="G113" s="11" t="n"/>
     </row>
     <row r="114" ht="64" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>T1550.001</t>
+          <t>T1555</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Use Alternate Authentication Material: Application Access Token</t>
+          <t>Credentials from Password Stores</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may use stolen application access tokens to authenticate to services without requiring passwords or MFA. Access tokens are often long-lived, may have broad permissions, and may not be protected as carefully as passwords. Stolen tokens can be obtained through malware, phishing, insecure storage, or compromised applications. Using stolen tokens allows fraud actors to bypass password-based authentication controls and may not trigger alerts for unusual login locations.</t>
+          <t>Fraud actors may search for common password storage locations to obtain user credentials. Passwords are stored in several places on a system, depending on the operating system or application holding the credentials. There are also specific applications and services that store passwords to make them easier for users to manage and maintain, such as password managers and cloud secrets vaults. Once credentials are obtained, they can be used to perform lateral movement and access restricted information.</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>TA0001</t>
+          <t>TA0043</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Initial Access</t>
+          <t>Reconnaissance</t>
         </is>
       </c>
       <c r="F114" s="11" t="n"/>
       <c r="G114" s="11" t="n"/>
     </row>
-    <row r="115" ht="64" customHeight="1">
+    <row r="115" ht="48" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>T1555</t>
+          <t>T1555.003</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Credentials from Password Stores</t>
+          <t>Credentials from Password Stores: Credentials from Web Browsers</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may search for common password storage locations to obtain user credentials. Passwords are stored in several places on a system, depending on the operating system or application holding the credentials. There are also specific applications and services that store passwords to make them easier for users to manage and maintain, such as password managers and cloud secrets vaults. Once credentials are obtained, they can be used to perform lateral movement and access restricted information.</t>
+          <t>Fraud actors may extract credentials saved in web browser password storage mechanisms. Web browsers commonly offer to save and autofill credentials for user convenience, but this stored information can be extracted by malware or fraud actors with local access. Extracted credentials may include usernames, passwords, and authentication tokens for various online services.</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -4017,90 +4017,90 @@
       <c r="F115" s="11" t="n"/>
       <c r="G115" s="11" t="n"/>
     </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>T1555.003</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Credentials from Password Stores: Credentials from Web Browsers</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may extract credentials saved in web browser password storage mechanisms. Web browsers commonly offer to save and autofill credentials for user convenience, but this stored information can be extracted by malware or fraud actors with local access. Extracted credentials may include usernames, passwords, and authentication tokens for various online services.</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
+    <row r="116" ht="64" customHeight="1">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>T1555.005</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Credentials from Password Stores: Password Managers</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="inlineStr">
+        <is>
+          <t>Fraud actors may acquire user credentials or passkeys from third-party password managers. Password managers are applications designed to store user credentials or passkeys, normally in an encrypted database. Credentials and passkeys are typically accessible after a user provides a master password that unlocks the database. After the database is unlocked, these credentials and passkeys may be copied to memory. These databases can be stored as files on disk.</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="inlineStr">
         <is>
           <t>TA0043</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E116" s="22" t="inlineStr">
         <is>
           <t>Reconnaissance</t>
         </is>
       </c>
-      <c r="F116" s="11" t="n"/>
-      <c r="G116" s="11" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n">
+        <v>46294.5</v>
+      </c>
     </row>
     <row r="117" ht="64" customHeight="1">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>T1555.005</t>
-        </is>
-      </c>
-      <c r="B117" s="20" t="inlineStr">
-        <is>
-          <t>Credentials from Password Stores: Password Managers</t>
-        </is>
-      </c>
-      <c r="C117" s="22" t="inlineStr">
-        <is>
-          <t>Fraud actors may acquire user credentials or passkeys from third-party password managers. Password managers are applications designed to store user credentials or passkeys, normally in an encrypted database. Credentials and passkeys are typically accessible after a user provides a master password that unlocks the database. After the database is unlocked, these credentials and passkeys may be copied to memory. These databases can be stored as files on disk.</t>
-        </is>
-      </c>
-      <c r="D117" s="22" t="inlineStr">
-        <is>
-          <t>TA0043</t>
-        </is>
-      </c>
-      <c r="E117" s="22" t="inlineStr">
-        <is>
-          <t>Reconnaissance</t>
-        </is>
-      </c>
-      <c r="F117" s="25" t="n"/>
-      <c r="G117" s="25" t="n">
-        <v>46294.5</v>
-      </c>
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>T1557</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Adversary-in-the-Middle</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may attempt to position themselves between two or more devices to support follow-on behaviors such as Network Sniffing, Transmitted Data Manipulation, or replay attacks (Exploitation for Credential Access). By abusing features of common network protocols that can determine the flow of network traffic (e.g. ARP, DNS, LLMNR, etc.), fraud actors may force a device to communicate through a fraudster-controlled system so they can collect information or perform additional actions.</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>TA0001, FA0001, TA0002</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>Initial Access, Positioning, Execution</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="n"/>
+      <c r="G117" s="11" t="n"/>
     </row>
     <row r="118" ht="64" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>T1557</t>
+          <t>T1583</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Adversary-in-the-Middle</t>
+          <t>Acquire Infrastructure</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may attempt to position themselves between two or more devices to support follow-on behaviors such as Network Sniffing, Transmitted Data Manipulation, or replay attacks (Exploitation for Credential Access). By abusing features of common network protocols that can determine the flow of network traffic (e.g. ARP, DNS, LLMNR, etc.), fraud actors may force a device to communicate through a fraudster-controlled system so they can collect information or perform additional actions.</t>
+          <t>Fraud actors may acquire or compromise infrastructure to support fraud operations. This may include registering domains, establishing hosting services, deploying command and control infrastructure, or compromising legitimate infrastructure for malicious use. Acquired infrastructure provides fraud actors with resources needed to conduct phishing campaigns, host malicious content, process fraudulent transactions, or maintain persistent access to compromised environments.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>TA0001, FA0001, TA0002</t>
+          <t>TA0042</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>Initial Access, Positioning, Execution</t>
+          <t>Resource Development</t>
         </is>
       </c>
       <c r="F118" s="11" t="n"/>
@@ -4109,17 +4109,17 @@
     <row r="119" ht="64" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>T1583</t>
+          <t>T1583.001</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Acquire Infrastructure</t>
+          <t>Acquire Infrastructure: Domains</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may acquire or compromise infrastructure to support fraud operations. This may include registering domains, establishing hosting services, deploying command and control infrastructure, or compromising legitimate infrastructure for malicious use. Acquired infrastructure provides fraud actors with resources needed to conduct phishing campaigns, host malicious content, process fraudulent transactions, or maintain persistent access to compromised environments.</t>
+          <t>Fraud actors may register domains similar to legitimate organizations or services to support fraud operations. This may include typosquatting domains, domains using different top-level domains, or domains incorporating organization names with additional words. Fraudulent domains are used for phishing websites, fake service websites, or to send emails that appear to originate from legitimate organizations.</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -4135,20 +4135,20 @@
       <c r="F119" s="11" t="n"/>
       <c r="G119" s="11" t="n"/>
     </row>
-    <row r="120" ht="64" customHeight="1">
+    <row r="120" ht="48" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>T1583.001</t>
+          <t>T1583.003</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Acquire Infrastructure: Domains</t>
+          <t>Acquire Infrastructure: Virtual Private Network or Server</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may register domains similar to legitimate organizations or services to support fraud operations. This may include typosquatting domains, domains using different top-level domains, or domains incorporating organization names with additional words. Fraudulent domains are used for phishing websites, fake service websites, or to send emails that appear to originate from legitimate organizations.</t>
+          <t>Fraud actors may acquire access to VPN services or anonymous proxy servers to mask their activities or create the appearance of legitimate operations. VPN and proxy services allow fraud actors to obscure their true location, bypass geographic restrictions, evade detection systems that rely on IP reputation, or simulate legitimate user traffic patterns during fraud operations.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -4164,140 +4164,111 @@
       <c r="F120" s="11" t="n"/>
       <c r="G120" s="11" t="n"/>
     </row>
-    <row r="121" ht="48" customHeight="1">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>T1583.003</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>Acquire Infrastructure: Virtual Private Network or Server</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may acquire access to VPN services or anonymous proxy servers to mask their activities or create the appearance of legitimate operations. VPN and proxy services allow fraud actors to obscure their true location, bypass geographic restrictions, evade detection systems that rely on IP reputation, or simulate legitimate user traffic patterns during fraud operations.</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
+    <row r="121" ht="64" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>T1583.008</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>Acquire Infrastructure: Malvertising</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>Fraud actors may create malicious advertisements that direct users to fraudulent sites equipped with credential harvesting or payment card skimming capabilities. This may include advertisements for fraudulent merchant sites, compromised legitimate merchant sites, and fradulent Whatsapp investment groups. Fraud actors often use stolen payment card data to fund advertising campaigns, creating a self-sustaining fraud operation where stolen credentials fund further credential theft activities.</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr">
+      <c r="E121" s="19" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F121" s="11" t="n"/>
-      <c r="G121" s="11" t="n"/>
-    </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="19" t="inlineStr">
-        <is>
-          <t>T1583.008</t>
-        </is>
-      </c>
-      <c r="B122" s="19" t="inlineStr">
-        <is>
-          <t>Acquire Infrastructure: Malvertising</t>
-        </is>
-      </c>
-      <c r="C122" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors may create malicious advertisements that direct users to fraudulent sites equipped with credential harvesting or payment card skimming capabilities. This may include advertisements for fraudulent merchant sites, compromised legitimate merchant sites, and fradulent Whatsapp investment groups. Fraud actors often use stolen payment card data to fund advertising campaigns, creating a self-sustaining fraud operation where stolen credentials fund further credential theft activities.</t>
-        </is>
-      </c>
-      <c r="D122" s="19" t="inlineStr">
-        <is>
-          <t>TA0042</t>
-        </is>
-      </c>
-      <c r="E122" s="19" t="inlineStr">
-        <is>
-          <t>Resource Development</t>
-        </is>
-      </c>
-      <c r="F122" s="24" t="n"/>
-      <c r="G122" s="24" t="n"/>
-    </row>
-    <row r="123" ht="208" customHeight="1">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="F121" s="24" t="n"/>
+      <c r="G121" s="24" t="n"/>
+    </row>
+    <row r="122" ht="208" customHeight="1">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>T1585</t>
         </is>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B122" s="9" t="inlineStr">
         <is>
           <t>Establish Accounts</t>
         </is>
       </c>
-      <c r="C123" s="9" t="inlineStr">
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may create and cultivate accounts with services that can be used during targeting. fraud actors can create accounts that can be used to build a persona to further operations. Persona development consists of the development of public information, presence, history and appropriate affiliations. This development could be applied to social media, website, or other publicly available information that could be referenced and scrutinized for legitimacy over the course of an operation using that persona or identity.
 For operations incorporating social engineering, the utilization of an online persona may be important. These personas may be fictitious or impersonate real people. The persona may exist on a single site or across multiple sites (ex: Facebook, LinkedIn, Twitter, Google, GitHub, Docker Hub, etc.). Establishing a persona may require development of additional documentation to make them seem real. This could include filling out profile information, developing social networks, or incorporating photos.
 Establishing accounts can also include the creation of accounts with email providers, which may be directly leveraged for Phishing for Information or Phishing. In addition, establishing accounts may allow fraud actors to abuse free services, such as registering for trial periods to Acquire Infrastructure for malicious purposes.</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E123" s="9" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F123" s="11" t="n"/>
-      <c r="G123" s="11" t="n"/>
-    </row>
-    <row r="124" ht="80" customHeight="1">
-      <c r="A124" s="18" t="inlineStr">
+      <c r="F122" s="11" t="n"/>
+      <c r="G122" s="11" t="n"/>
+    </row>
+    <row r="123" ht="80" customHeight="1">
+      <c r="A123" s="18" t="inlineStr">
         <is>
           <t>T1585.004</t>
         </is>
       </c>
-      <c r="B124" s="18" t="inlineStr">
+      <c r="B123" s="18" t="inlineStr">
         <is>
           <t>Establish Accounts: Dating App Accounts</t>
         </is>
       </c>
-      <c r="C124" s="21" t="inlineStr">
+      <c r="C123" s="21" t="inlineStr">
         <is>
           <t>Fraud actors may create and cultivate accounts on dating applications or relationship-oriented platforms to build fraudulent personas and establish trust with potential victims. They may populate profiles with fabricated biographical details, stolen or synthetic images, and sustained messaging histories, then develop relationships that support romance, investment, payment, credential-theft, or other fraud schemes. These accounts may be operated individually or at scale and may direct victims to other communication or payment channels.</t>
         </is>
       </c>
-      <c r="D124" s="21" t="inlineStr">
+      <c r="D123" s="21" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E124" s="21" t="inlineStr">
+      <c r="E123" s="21" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F124" s="23" t="n">
+      <c r="F123" s="23" t="n">
         <v>46255.5</v>
       </c>
-      <c r="G124" s="23" t="n">
+      <c r="G123" s="23" t="n">
         <v>46255.5</v>
       </c>
     </row>
-    <row r="125" ht="240" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
+    <row r="124" ht="240" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>T1586</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
         <is>
           <t>Compromise Accounts</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>Fraud Actors may compromise accounts with services that can be used during targeting. For operations incorporating social engineering, the utilization of an online persona may be important. Rather than creating and cultivating accounts (i.e. Establish Accounts), adversaries may compromise existing accounts. Utilizing an existing persona may engender a level of trust in a potential victim if they have a relationship, or knowledge of, the compromised persona.
 A variety of methods exist for compromising accounts, such as gathering credentials via Phishing for Information, purchasing credentials from third-party sites, brute forcing credentials (ex: password reuse from breach credential dumps), or paying employees, suppliers or business partners for access to credentials.Prior to compromising accounts, adversaries may conduct Reconnaissance to inform decisions about which accounts to compromise to further their operation.
@@ -4305,31 +4276,31 @@
 Fraud actors may directly leverage compromised email accounts for Phishing for Information or Phishing.</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F125" s="11" t="n"/>
-      <c r="G125" s="11" t="n"/>
-    </row>
-    <row r="126" ht="272" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="F124" s="11" t="n"/>
+      <c r="G124" s="11" t="n"/>
+    </row>
+    <row r="125" ht="272" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>T1586.001</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>Compromise Accounts: Social Media Accounts</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>Adversaries may compromise social media accounts that can be used during targeting. For operations incorporating social engineering, the utilization of an online persona may be important. Rather than creating and cultivating social media profiles (i.e. Social Media Accounts), adversaries may compromise existing social media accounts. Utilizing an existing persona may engender a level of trust in a potential victim if they have a relationship, or knowledge of, the compromised persona.
 A variety of methods exist for compromising social media accounts, such as gathering credentials via Phishing for Information, purchasing credentials from third-party sites, or by brute forcing credentials (ex: password reuse from breach credential dumps). Prior to compromising social media accounts, adversaries may conduct Reconnaissance to inform decisions about which accounts to compromise to further their operation.
@@ -4337,129 +4308,159 @@
 Adversaries can use a compromised social media profile to create new, or hijack existing, connections to targets of interest. These connections may be direct or may include trying to connect through others. Compromised profiles may be leveraged during other phases of the adversary lifecycle, such as during Initial Access (ex: Spearphishing via Service).</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F126" s="11" t="n"/>
-      <c r="G126" s="11" t="n"/>
-    </row>
-    <row r="127" ht="224" customHeight="1">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="F125" s="11" t="n"/>
+      <c r="G125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="224" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>T1586.002</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>Compromise Accounts: Email Accounts</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may compromise email accounts that can be used during targeting. Fraud actors can use compromised email accounts to further their operations, such as leveraging them to conduct Phishing for Information, Phishing, or large-scale spam email campaigns. Utilizing an existing persona with a compromised email account may engender a level of trust in a potential victim if they have a relationship with, or knowledge of, the compromised persona. Compromised email accounts can also be used in the acquisition of infrastructure (ex: Domains).
 A variety of methods exist for compromising email accounts, such as gathering credentials via Phishing for Information, purchasing credentials from third-party sites, brute forcing credentials (ex: password reuse from breach credential dumps), or paying employees, suppliers or business partners for access to credentials. Prior to compromising email accounts, fraud actors may conduct Reconnaissance to inform decisions about which accounts to compromise to further their operation. Fraud actors may target compromising well-known email accounts or domains from which malicious spam or Phishing emails may evade reputation-based email filtering rules.
 Fraud actors can use a compromised email account to hijack existing email threads with targets of interest.</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F127" s="11" t="n"/>
-      <c r="G127" s="11" t="n"/>
-    </row>
-    <row r="128" ht="192" customHeight="1">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="F126" s="11" t="n"/>
+      <c r="G126" s="11" t="n"/>
+    </row>
+    <row r="127" ht="192" customHeight="1">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>T1586.003</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>Compromise Accounts: Cloud Accounts</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Fraud Actors may compromise cloud accounts that can be used during targeting. Adversaries can use compromised cloud accounts to further their operations, including leveraging cloud storage services such as Dropbox, Microsoft OneDrive, or AWS S3 buckets for Exfiltration to Cloud Storage or to Upload Tools. Cloud accounts can also be used in the acquisition of infrastructure, such as Virtual Private Servers or Serverless infrastructure. Additionally, cloud-based messaging services such as Twilio, SendGrid, AWS End User Messaging, AWS SNS (Simple Notification Service), or AWS SES (Simple Email Service) may be leveraged for spam or Phishing. Compromising cloud accounts may allow adversaries to develop sophisticated capabilities without managing their own servers.
 A variety of methods exist for compromising cloud accounts, such as gathering credentials via Phishing for Information, purchasing credentials from third-party sites, conducting Password Spraying attacks, or attempting to Steal Application Access Tokens. Prior to compromising cloud accounts, adversaries may conduct Reconnaissance to inform decisions about which accounts to compromise to further their operation. In some cases, adversaries may target privileged service provider accounts with the intent of leveraging a Trusted Relationship between service providers and their customers.
 </t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F128" s="11" t="n"/>
-      <c r="G128" s="11" t="n"/>
-    </row>
-    <row r="129" ht="240" customHeight="1">
-      <c r="A129" s="14" t="inlineStr">
+      <c r="F127" s="11" t="n"/>
+      <c r="G127" s="11" t="n"/>
+    </row>
+    <row r="128" ht="240" customHeight="1">
+      <c r="A128" s="14" t="inlineStr">
         <is>
           <t>T1586.004</t>
         </is>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>Compromise Accounts: Corporate Accounts</t>
         </is>
       </c>
-      <c r="C129" s="12" t="inlineStr">
+      <c r="C128" s="12" t="inlineStr">
         <is>
           <t>Fraud actors may compromise corporate accounts that can be used during targeting and follow-on fraud operations. Compromised corporate accounts provide fraud actors with legitimate access to business systems, internal applications, and communication channels that can be leveraged to conduct business email compromise attacks, initiate unauthorized transactions, or modify business processes for financial gain.
 A variety of methods exist for compromising corporate accounts, such as gathering credentials via Phishing for Information, purchasing credentials from third-party sites, brute forcing credentials (for example, password reuse from breach credential dumps), or paying employees, suppliers, or business partners for access to credentials. Prior to compromising corporate accounts, fraud actors may conduct Reconnaissance to identify high-value employees, roles, or business units whose access can provide entry to sensitive data, financial systems, or approval workflows.
 Once compromised, corporate accounts may be used to access internal systems, customer records, financial information, or other protected corporate resources, as well as to authorize fraudulent payments or make unauthorized changes to vendor, payroll, or billing details. Fraud actors may also further develop the compromised corporate identity, such as by maintaining normal email behavior or updating profiles, to preserve trust with partners and customers while they execute and expand their fraud schemes.</t>
         </is>
       </c>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="D128" s="12" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E129" s="12" t="inlineStr">
+      <c r="E128" s="12" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F129" s="13" t="n"/>
-      <c r="G129" s="13" t="n"/>
-    </row>
-    <row r="130" ht="144" customHeight="1">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="F128" s="13" t="n"/>
+      <c r="G128" s="13" t="n"/>
+    </row>
+    <row r="129" ht="144" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>T1593</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
         <is>
           <t>Search Open Websites/Domains</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may search freely available online sources for information about customers or organizations that can be used to plan and target fraud. This can include browsing social media profiles, public records, company websites, data‑leak forums, and other open sources to collect details such as contact information, roles, affiliations, and recent activity.
 They may tailor where they look based on the type of information needed—for example, using professional networks to identify finance staff, public procurement sites to learn about vendors and contracts, or social platforms to understand personal relationships and behaviors. Information gathered from open sources can then be used to craft convincing social‑engineering pretexts, identify high‑value accounts or employees, and enable follow‑on techniques such as phishing for information, establishing or compromising accounts, or attempting direct access to exposed services.</t>
         </is>
       </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>TA0043</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Reconnaissance</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="n"/>
+      <c r="G129" s="11" t="n"/>
+    </row>
+    <row r="130" ht="128" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>T1593.001</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Search Open Websites/Domains: Social Media</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Fraud actors may search social media platforms for information about customers or organizations that can be used to plan and target fraud. Public posts, profiles, and company pages can reveal details such as roles and seniority, contact information, locations, recent business events, and personal interests or relationships that make social‑engineering attempts more convincing.
+They may passively harvest data from multiple social networks or professional platforms, then use that information to tailor phishing messages, impersonate trusted contacts, or identify high‑value employees and accounts. Fraud actors may also create fake profiles, pages, or groups that mimic real people or organizations in order to build rapport and lure targets into disclosing additional details, which can then be used to support account takeover, new‑account fraud, or other targeted fraud operations.</t>
+        </is>
+      </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
           <t>TA0043</t>
@@ -4476,18 +4477,18 @@
     <row r="131" ht="128" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>T1593.001</t>
+          <t>T1593.002</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Search Open Websites/Domains: Social Media</t>
+          <t>Search Open Websites/Domains: Search Engines</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Fraud actors may search social media platforms for information about customers or organizations that can be used to plan and target fraud. Public posts, profiles, and company pages can reveal details such as roles and seniority, contact information, locations, recent business events, and personal interests or relationships that make social‑engineering attempts more convincing.
-They may passively harvest data from multiple social networks or professional platforms, then use that information to tailor phishing messages, impersonate trusted contacts, or identify high‑value employees and accounts. Fraud actors may also create fake profiles, pages, or groups that mimic real people or organizations in order to build rapport and lure targets into disclosing additional details, which can then be used to support account takeover, new‑account fraud, or other targeted fraud operations.</t>
+          <t>Fraud actors may use search engines to collect information about customers, employees, and organizations that can be leveraged for fraud. General queries can surface public details such as contact information, exposed documents, cached pages, and references to accounts or services tied to a target.
+They may also craft specialized queries (for example, using advanced operators or searching by file type) to locate accidentally exposed data, such as configuration files, credential lists, internal documents, or screenshots containing sensitive information. Insights gathered from search results can then be used to refine social‑engineering pretexts, identify weakly protected services, support account takeover or new‑account fraud, and guide further reconnaissance against specific people, systems, or business processes.</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -4503,198 +4504,168 @@
       <c r="F131" s="11" t="n"/>
       <c r="G131" s="11" t="n"/>
     </row>
-    <row r="132" ht="128" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>T1593.002</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="inlineStr">
-        <is>
-          <t>Search Open Websites/Domains: Search Engines</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>Fraud actors may use search engines to collect information about customers, employees, and organizations that can be leveraged for fraud. General queries can surface public details such as contact information, exposed documents, cached pages, and references to accounts or services tied to a target.
-They may also craft specialized queries (for example, using advanced operators or searching by file type) to locate accidentally exposed data, such as configuration files, credential lists, internal documents, or screenshots containing sensitive information. Insights gathered from search results can then be used to refine social‑engineering pretexts, identify weakly protected services, support account takeover or new‑account fraud, and guide further reconnaissance against specific people, systems, or business processes.</t>
-        </is>
-      </c>
-      <c r="D132" s="9" t="inlineStr">
-        <is>
-          <t>TA0043</t>
-        </is>
-      </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>Reconnaissance</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="n"/>
-      <c r="G132" s="11" t="n"/>
-    </row>
-    <row r="133" ht="224" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+    <row r="132" ht="224" customHeight="1">
+      <c r="A132" s="19" t="inlineStr">
         <is>
           <t>T1598</t>
         </is>
       </c>
-      <c r="B133" s="19" t="inlineStr">
+      <c r="B132" s="19" t="inlineStr">
         <is>
           <t>Phishing for Information</t>
         </is>
       </c>
-      <c r="C133" s="19" t="inlineStr">
+      <c r="C132" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may send phishing messages across multiple channels - email, SMS (smishing), QR codes (quishing), and voice calls (vishing) - to elicit sensitive information for targeting and follow‑on fraud. Phishing for information focuses on tricking targets into revealing credentials, one‑time passcodes, or other actionable data, and is distinct from Phishing, which primarily aims to get the user to execute malicious code or payloads.
 These are all electronically delivered social‑engineering attacks. Email phishing and spearphishing may target specific people or organizations, while broad campaigns support mass credential harvesting. Smishing uses deceptive texts, quishing uses QR codes that lead to fraudulent sites, and vishing relies on calls or voicemail to socially engineer victims, sometimes by luring them to dial a controlled phone number.
 Phishing for information typically uses convincing pretexts—such as posing as a bank, payment provider, help desk, or vendor—and often leverages urgency like account lockouts or security alerts. Attackers combine email spoofing, look‑alike domains, shortened links in SMS, and caller‑ID spoofing in vishing to appear legitimate, and may hide or manipulate messages, headers, sender IDs, or phone numbers to bypass security tools and reduce the chance of detection across email, SMS, QR, and voice channels.</t>
         </is>
       </c>
-      <c r="D133" s="19" t="inlineStr">
+      <c r="D132" s="19" t="inlineStr">
         <is>
           <t>TA0043</t>
         </is>
       </c>
-      <c r="E133" s="19" t="inlineStr">
+      <c r="E132" s="19" t="inlineStr">
         <is>
           <t>Reconnaissance</t>
         </is>
       </c>
-      <c r="F133" s="24" t="n"/>
-      <c r="G133" s="24" t="n"/>
-    </row>
-    <row r="134" ht="160" customHeight="1">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="F132" s="24" t="n"/>
+      <c r="G132" s="24" t="n"/>
+    </row>
+    <row r="133" ht="160" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>T1608</t>
         </is>
       </c>
-      <c r="B134" s="9" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>Stage Capabilities</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may upload, install, or otherwise set up capabilities and infrastructure that will be used in later stages of fraud operations. This can include staging tools and content they have developed or acquired on infrastructure they control, such as purchased or compromised servers, cloud platforms, or web services, as well as on third‑party platforms like app stores, code‑hosting sites, or social networks.
 Staging activities may involve hosting phishing or impersonation websites, configuring command‑and‑control or automation infrastructure, uploading malicious applications or scripts, or creating and populating social media profiles and other online personas for fraud operations. Fraud actors may also stage payloads, tooling, and supporting web resources used to deliver links or files in phishing campaigns, to enable later tool transfer into victim environments, or to support encrypted communications and other operational needs. Collectively, these actions position the technical resources required to execute and sustain fraud at scale.</t>
         </is>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F134" s="11" t="n"/>
-      <c r="G134" s="11" t="n"/>
+      <c r="F133" s="11" t="n"/>
+      <c r="G133" s="11" t="n"/>
+    </row>
+    <row r="134" ht="64" customHeight="1">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>T1608.006</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>Stage Capabilities: SEO Poisoning</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>Fraud actors may manipulate search engine optimization to position malicious websites prominently in search results for targeted keywords. SEO poisoning can make fraudulent websites, phishing pages, or malicious content appear in top search results for legitimate queries. This technique exploits user trust in search engines and may target users searching for customer service contact information, software downloads, or financial services.</t>
+        </is>
+      </c>
+      <c r="D134" s="19" t="inlineStr">
+        <is>
+          <t>TA0042</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>Resource Development</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="n"/>
+      <c r="G134" s="24" t="n"/>
     </row>
     <row r="135" ht="64" customHeight="1">
       <c r="A135" s="19" t="inlineStr">
         <is>
-          <t>T1608.006</t>
+          <t>T1621</t>
         </is>
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>Stage Capabilities: SEO Poisoning</t>
+          <t>Multi-Factor Authentication Request Generation</t>
         </is>
       </c>
       <c r="C135" s="19" t="inlineStr">
         <is>
-          <t>Fraud actors may manipulate search engine optimization to position malicious websites prominently in search results for targeted keywords. SEO poisoning can make fraudulent websites, phishing pages, or malicious content appear in top search results for legitimate queries. This technique exploits user trust in search engines and may target users searching for customer service contact information, software downloads, or financial services.</t>
+          <t>Fraud actors may generate multiple MFA requests to overwhelm or pressure victims into approving fraudulent authentication attempts. This technique, often called MFA fatigue, involves repeatedly generating authentication requests until the victim approves access to stop the notifications. Fraud actors rely on user frustration, confusion, or mistakes to gain approval for unauthorized access attempts.</t>
         </is>
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t>TA0042</t>
+          <t>TA0001</t>
         </is>
       </c>
       <c r="E135" s="19" t="inlineStr">
         <is>
-          <t>Resource Development</t>
+          <t>Initial Access</t>
         </is>
       </c>
       <c r="F135" s="24" t="n"/>
       <c r="G135" s="24" t="n"/>
     </row>
-    <row r="136" ht="64" customHeight="1">
-      <c r="A136" s="19" t="inlineStr">
-        <is>
-          <t>T1621</t>
-        </is>
-      </c>
-      <c r="B136" s="19" t="inlineStr">
-        <is>
-          <t>Multi-Factor Authentication Request Generation</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>Fraud actors may generate multiple MFA requests to overwhelm or pressure victims into approving fraudulent authentication attempts. This technique, often called MFA fatigue, involves repeatedly generating authentication requests until the victim approves access to stop the notifications. Fraud actors rely on user frustration, confusion, or mistakes to gain approval for unauthorized access attempts.</t>
-        </is>
-      </c>
-      <c r="D136" s="19" t="inlineStr">
-        <is>
-          <t>TA0001</t>
-        </is>
-      </c>
-      <c r="E136" s="19" t="inlineStr">
-        <is>
-          <t>Initial Access</t>
-        </is>
-      </c>
-      <c r="F136" s="24" t="n"/>
-      <c r="G136" s="24" t="n"/>
-    </row>
-    <row r="137" ht="240" customHeight="1">
-      <c r="A137" s="9" t="inlineStr">
+    <row r="136" ht="240" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>T1650</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B136" s="9" t="inlineStr">
         <is>
           <t>Acquire Access</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may purchase or otherwise obtain existing access to organizations, accounts, or infrastructure instead of gaining access themselves. This access is often sold through underground markets or broker networks and can include compromised bank and customer accounts, merchant accounts, remote access into back‑office systems, or logins to third‑party platforms that process payments or store customer data.
 Purchased access may take many forms, such as credentials and MFA artifacts for online banking or payment accounts, administrative access to merchant portals, remote access tools already deployed on internal systems, or API keys and tokens that allow programmatic control of financial services. Brokers may also pre‑install tooling or “loads” that buyers can use to deploy additional malware or automate fraud at scale.
 By leveraging acquired access, fraud actors can bypass early intrusion steps and focus on high‑value fraud activity such as moving funds, altering account details, manipulating transactions, or harvesting additional identities and credentials. They may prioritize buying access to accounts or systems with high limits, weak monitoring, or privileged roles, and to organizations in sectors (for example, processors, fintechs, BPOs, or service providers) where a single foothold can be used to reach additional victims through trusted business relationships and shared platforms.</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>TA0042</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
+      <c r="E136" s="9" t="inlineStr">
         <is>
           <t>Resource Development</t>
         </is>
       </c>
-      <c r="F137" s="11" t="n"/>
-      <c r="G137" s="11" t="n"/>
-    </row>
-    <row r="138" ht="365" customHeight="1">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="F136" s="11" t="n"/>
+      <c r="G136" s="11" t="n"/>
+    </row>
+    <row r="137" ht="365" customHeight="1">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>T1660</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>Phishing</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
         <is>
           <t>Fraud Actors may send malicious content to users in order to gain access to their mobile devices. All forms of phishing are electronically delivered social engineering. Adversaries can conduct both non-targeted phishing, such as in mass malware spam campaigns, as well as more targeted phishing tailored for a specific individual, company, or industry, known as "spearphishing." Phishing often involves social engineering techniques, such as posing as a trusted source, as well as evasion techniques, such as removing or manipulating emails or metadata/headers from compromised accounts being abused to send messages.
 Mobile phishing may take various forms. For example, adversaries may send emails containing malicious attachments or links, typically to deliver and then execute malicious code on victim devices. Phishing may also be conducted via third-party services, like social media platforms. Adversaries may also impersonate executives of organizations to persuade victims into performing some action on their behalf. For example, adversaries will often use social engineering techniques in text messages to trick the victims into acting quickly, which leads to adversaries obtaining credentials and other information.
@@ -4704,79 +4675,79 @@
 - Phone Calls: Adversaries may call victims (known as "vishing") to persuade them to perform an action, such as providing login credentials or navigating to a malicious website. This could also be used as a technique to perform the initial access on a mobile device, but then pivot to a computer/other network by having the victim perform an action on a desktop computer.</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>TA0001</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>Initial Access</t>
         </is>
       </c>
-      <c r="F138" s="11" t="n"/>
-      <c r="G138" s="11" t="n"/>
-    </row>
-    <row r="139" ht="160" customHeight="1">
-      <c r="A139" s="19" t="inlineStr">
+      <c r="F137" s="11" t="n"/>
+      <c r="G137" s="11" t="n"/>
+    </row>
+    <row r="138" ht="160" customHeight="1">
+      <c r="A138" s="19" t="inlineStr">
         <is>
           <t>T1667</t>
         </is>
       </c>
-      <c r="B139" s="19" t="inlineStr">
+      <c r="B138" s="19" t="inlineStr">
         <is>
           <t>Email Bombing</t>
         </is>
       </c>
-      <c r="C139" s="19" t="inlineStr">
+      <c r="C138" s="19" t="inlineStr">
         <is>
           <t>Fraud actors may flood targeted email addresses with an overwhelming volume of messages. This may bury legitimate emails in a flood of spam and disrupt business operations.
 A fraud actor may accomplish email bombing by leveraging an automated bot to register a targeted address for e-mail lists that do not validate new signups, such as online newsletters. The result can be a wave of thousands of e-mails that effectively overloads the victim’s inbox.
 By sending hundreds or thousands of e-mails in quick succession, fraud actors may successfully divert attention away from and bury legitimate messages including security alerts, daily business processes like help desk tickets and client correspondence, or ongoing scams. This behavior can also be used as a tool of harassment.</t>
         </is>
       </c>
-      <c r="D139" s="19" t="inlineStr">
+      <c r="D138" s="19" t="inlineStr">
         <is>
           <t>TA0112</t>
         </is>
       </c>
-      <c r="E139" s="19" t="inlineStr">
+      <c r="E138" s="19" t="inlineStr">
         <is>
           <t>Defense Impairment</t>
         </is>
       </c>
-      <c r="F139" s="24" t="n"/>
-      <c r="G139" s="24" t="n"/>
-    </row>
-    <row r="140" ht="128" customHeight="1">
-      <c r="A140" s="9" t="inlineStr">
+      <c r="F138" s="24" t="n"/>
+      <c r="G138" s="24" t="n"/>
+    </row>
+    <row r="139" ht="128" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>T1672</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>Email Spoofing</t>
         </is>
       </c>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="C139" s="9" t="inlineStr">
         <is>
           <t>Fraud actors may forge or misrepresent the sender’s email address and related headers so messages appear to come from a trusted or recognizable source, such as a bank, employer, vendor, or colleague. The goal is to make the email look legitimate enough that recipients will trust the content and act on it.
 Spoofed emails are commonly used in phishing and fraud schemes to convince victims to click links, open attachments, share credentials or other sensitive information, change payment details, or approve fraudulent transactions. By imitating known domains, display names, or reply‑to addresses - and sometimes bypassing basic email authentication controls - email spoofing increases the likelihood that fraudulent messages evade suspicion and technical defenses.</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
         <is>
           <t>TA0005</t>
         </is>
       </c>
-      <c r="E140" s="9" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>Stealth</t>
         </is>
       </c>
-      <c r="F140" s="11" t="n"/>
-      <c r="G140" s="11" t="n"/>
+      <c r="F139" s="11" t="n"/>
+      <c r="G139" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
